--- a/reports/2026-07-31/blotter_report.xlsx
+++ b/reports/2026-07-31/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$233</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -519,12 +519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BEVCENTER</t>
+          <t>ABQUP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beverly Center</t>
+          <t>ABQ Uptown</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -547,12 +547,8 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>111.8</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>46214.80486111111</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="b">
         <v>0</v>
       </c>
@@ -560,12 +556,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>BEVCENTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Beverly Center</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -574,25 +570,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>25.7</v>
+        <v>111.8</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46231.83333333334</v>
+        <v>46214.80486111111</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -601,12 +597,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,25 +611,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>186.3</v>
+        <v>151.4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46232.0625</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -642,36 +638,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>Cherry Creek Shopping Center</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>46231.83333333334</v>
+      </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
@@ -679,12 +679,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -693,25 +693,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>145.2</v>
+        <v>186.3</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46232.82986111111</v>
+        <v>46232.0625</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -720,40 +720,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>Lenox Square</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>46231.92430555556</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="b">
         <v>0</v>
       </c>
@@ -761,42 +757,165 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Domain</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>Northgate Station</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>46232.82986111111</v>
+      </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OPRYMILLS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Opry Mills</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>54</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>46231.92430555556</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>73</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>47</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23</v>
+      </c>
+      <c r="I10" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>THEDOMAIN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The Domain</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1072,30 +1191,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DP2026357948121100</t>
+          <t>20260723-0938-05</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46204.69791666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>robbery-bank</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1105,56 +1224,56 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>robbery</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3410 E 1ST AVE</t>
+          <t>6600 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>39.71748838438504</v>
+        <v>35.14845720336839</v>
       </c>
       <c r="K5" t="n">
-        <v>-104.946995728207</v>
+        <v>-80.83089079594687</v>
       </c>
       <c r="L5" t="n">
-        <v>497.7</v>
+        <v>383.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 15, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260723-0938-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>71712344706</t>
+          <t>DP2026357948121100</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46220.41458333333</v>
+        <v>46204.69791666666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Weapon Law Violations</t>
+          <t>robbery-bank</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1164,56 +1283,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>robbery</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>3410 E 1ST AVE</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>47.708569</v>
+        <v>39.71748838438504</v>
       </c>
       <c r="K6" t="n">
-        <v>-122.319207</v>
+        <v>-104.946995728207</v>
       </c>
       <c r="L6" t="n">
-        <v>539</v>
+        <v>497.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DP2026403380131300</t>
+          <t>71712344706</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46225.54166666666</v>
+        <v>46220.41458333333</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Weapon Law Violations</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1223,56 +1342,56 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>300 BLOCK N ST PAUL ST</t>
+          <t>8XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.72175920473841</v>
+        <v>47.708569</v>
       </c>
       <c r="K7" t="n">
-        <v>-104.9509152755314</v>
+        <v>-122.319207</v>
       </c>
       <c r="L7" t="n">
-        <v>566.4</v>
+        <v>539</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71584399485</t>
+          <t>DP2026403380131300</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46214.825</v>
+        <v>46225.54166666666</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1282,56 +1401,56 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5TH AVE NE / NE 103RD ST</t>
+          <t>300 BLOCK N ST PAUL ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.70314032</v>
+        <v>39.72175920473841</v>
       </c>
       <c r="K8" t="n">
-        <v>-122.323148370417</v>
+        <v>-104.9509152755314</v>
       </c>
       <c r="L8" t="n">
-        <v>596.2</v>
+        <v>566.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260449391_11</t>
+          <t>71584399485</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46227.02291666667</v>
+        <v>46214.825</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BURGLARY- AGGRAVATED</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1341,56 +1460,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Unarmed</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GRAYBAR</t>
+          <t>5TH AVE NE / NE 103RD ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36.10999999969955</v>
+        <v>47.70314032</v>
       </c>
       <c r="K9" t="n">
-        <v>-86.81000000032267</v>
+        <v>-122.323148370417</v>
       </c>
       <c r="L9" t="n">
-        <v>630.5</v>
+        <v>596.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Burglary- aggravated on Jul 24, 2026, 631 m from The Mall at Green Hills (GRAYBAR). Weapon: Unarmed. Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260449391 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>GREENHILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71783099253</t>
+          <t>20260449391_11</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46214.86041666667</v>
+        <v>46227.02291666667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Weapon Law Violations</t>
+          <t>BURGLARY- AGGRAVATED</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1400,56 +1519,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Unarmed</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ROOSEVELT WAY NE / NE NORTHGATE WAY</t>
+          <t>GRAYBAR</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.70856098</v>
+        <v>36.10999999969955</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.317852210813</v>
+        <v>-86.81000000032267</v>
       </c>
       <c r="L10" t="n">
-        <v>639.8</v>
+        <v>630.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary- aggravated on Jul 24, 2026, 631 m from The Mall at Green Hills (GRAYBAR). Weapon: Unarmed. Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260449391 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>71783099253</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46229.1125</v>
+        <v>46214.86041666667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Weapon Law Violations</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1459,56 +1578,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>ROOSEVELT WAY NE / NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>39.71130989687384</v>
+        <v>47.70856098</v>
       </c>
       <c r="K11" t="n">
-        <v>-104.9490029653731</v>
+        <v>-122.317852210813</v>
       </c>
       <c r="L11" t="n">
-        <v>696.3</v>
+        <v>639.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20260413668_11</t>
+          <t>20260722-2124-02</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46208.92083333333</v>
+        <v>46225.16666666666</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASSAULT- FEAR OF BODILY INJURY</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1516,54 +1635,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2011 2011</t>
+          <t>9400 STEELE CREEK RD</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>36.10400000035705</v>
+        <v>35.16250902126527</v>
       </c>
       <c r="K12" t="n">
-        <v>-86.81000000032267</v>
+        <v>-80.96982377170991</v>
       </c>
       <c r="L12" t="n">
-        <v>702.5</v>
+        <v>647.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault- fear of bodily injury on Jul 05, 2026, 702 m from The Mall at Green Hills (2011 2011). Premises: APARTMENT. Status: REFUSED TO COOPERATE. Victims: 1. Flags: domestic related. Case #20260413668 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 22, 2026, 648 m from Charlotte Premium Outlets (9400 STEELE CREEK RD). Status: Open. Case #20260722-2124-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71275287160</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46205.52083333334</v>
+        <v>46229.1125</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1573,52 +1696,52 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>117XX BLOCK OF 5TH AVE NE</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.71495242</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.323460201162</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L13" t="n">
-        <v>798.3</v>
+        <v>696.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>GREENHILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260423135_11</t>
+          <t>20260413668_11</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46214.05208333334</v>
+        <v>46208.92083333333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1633,51 +1756,51 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OPRYLAND</t>
+          <t>2011 2011</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36.20999999970633</v>
+        <v>36.10400000035705</v>
       </c>
       <c r="K14" t="n">
-        <v>-86.69000000027951</v>
+        <v>-86.81000000032267</v>
       </c>
       <c r="L14" t="n">
-        <v>808.3</v>
+        <v>702.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault- fear of bodily injury on Jul 05, 2026, 702 m from The Mall at Green Hills (2011 2011). Premises: APARTMENT. Status: REFUSED TO COOPERATE. Victims: 1. Flags: domestic related. Case #20260413668 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260440008_11</t>
+          <t>71275287160</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46222.99930555555</v>
+        <v>46205.52083333334</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Assault, Aggravated - Deadly Weapon - Int/Kn</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1687,26 +1810,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HANDGUN</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2902 2902</t>
+          <t>117XX BLOCK OF 5TH AVE NE</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36.20599999976586</v>
+        <v>47.71495242</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.70200000037366</v>
+        <v>-122.323460201162</v>
       </c>
       <c r="L15" t="n">
-        <v>936.3</v>
+        <v>798.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1728,15 +1851,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260440008_22</t>
+          <t>20260423135_11</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46222.99930555555</v>
+        <v>46214.05208333334</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASSAULT- OFFENSIVE OR PROVOCATIVE CONTACT</t>
+          <t>ASSAULT- FEAR OF BODILY INJURY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1744,58 +1867,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>PERSONAL (HANDS)</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2902 2902</t>
+          <t>OPRYLAND</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>36.20599999976586</v>
+        <v>36.20999999970633</v>
       </c>
       <c r="K16" t="n">
-        <v>-86.70200000037366</v>
+        <v>-86.69000000027951</v>
       </c>
       <c r="L16" t="n">
-        <v>936.3</v>
+        <v>808.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260440008_33</t>
+          <t>20260725-0853-00</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46222.99930555555</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WEAPON OFFENSE, CRIMINAL ATTEMPT</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1805,56 +1924,56 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HANDGUN</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2902 2902</t>
+          <t>5700 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>36.20599999976586</v>
+        <v>35.15368289092867</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.70200000037366</v>
+        <v>-80.8398453262274</v>
       </c>
       <c r="L17" t="n">
-        <v>936.3</v>
+        <v>877.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>20260722-0920-00</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46230.4375</v>
+        <v>46225.16666666666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1864,262 +1983,262 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>5300 SHARON RD</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.70504225</v>
+        <v>35.14420159566059</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.338094779232</v>
+        <v>-80.83298000600156</v>
       </c>
       <c r="L18" t="n">
-        <v>938.8</v>
+        <v>885.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 22, 2026, 885 m from Southpark (5300 SHARON RD). Status: Exceptionally Cleared. Case #20260722-0920-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DP20266009882230300</t>
+          <t>20260440008_11</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46224.63194444445</v>
+        <v>46222.99930555555</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Assault, Aggravated - Deadly Weapon - Int/Kn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>HANDGUN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>2902 2902</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>39.71700581534508</v>
+        <v>36.20599999976586</v>
       </c>
       <c r="K19" t="n">
-        <v>-104.9529964927036</v>
+        <v>-86.70200000037366</v>
       </c>
       <c r="L19" t="n">
-        <v>25.7</v>
+        <v>936.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DP20266009631230800</t>
+          <t>20260440008_22</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46218.5625</v>
+        <v>46222.99930555555</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>theft-from-bldg</t>
+          <t>ASSAULT- OFFENSIVE OR PROVOCATIVE CONTACT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PERSONAL (HANDS)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>2902 2902</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>39.71700581534508</v>
+        <v>36.20599999976586</v>
       </c>
       <c r="K20" t="n">
-        <v>-104.9529964927036</v>
+        <v>-86.70200000037366</v>
       </c>
       <c r="L20" t="n">
-        <v>25.7</v>
+        <v>936.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DP20266009395230300</t>
+          <t>20260440008_33</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46212.80555555555</v>
+        <v>46222.99930555555</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>WEAPON OFFENSE, CRIMINAL ATTEMPT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>HANDGUN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>2902 2902</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39.71700581534508</v>
+        <v>36.20599999976586</v>
       </c>
       <c r="K21" t="n">
-        <v>-104.9529964927036</v>
+        <v>-86.70200000037366</v>
       </c>
       <c r="L21" t="n">
-        <v>25.7</v>
+        <v>936.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DP2026380800230300</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46212.60416666666</v>
+        <v>46230.4375</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>39.71700581534508</v>
+        <v>47.70504225</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.9529964927036</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L22" t="n">
-        <v>25.7</v>
+        <v>938.8</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2141,11 +2260,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DP2026376323230300</t>
+          <t>DP20266009882230300</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>46211.75277777778</v>
+        <v>46224.63194444445</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2178,7 +2297,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 08, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026376323 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2200,15 +2319,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DP20266009170230300</t>
+          <t>DP20266009631230800</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46208.67916666667</v>
+        <v>46218.5625</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>theft-from-bldg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2237,7 +2356,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 05, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009170 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2259,11 +2378,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DP20266009209230300</t>
+          <t>DP20266009395230300</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46205.70972222222</v>
+        <v>46212.80555555555</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2296,7 +2415,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 02, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009209 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2318,15 +2437,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DP2026399148239900</t>
+          <t>DP2026380800230300</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46223.54652777778</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>theft-other</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2341,21 +2460,21 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3030 E 1ST AVE</t>
+          <t>3000 E 1ST AVE</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>39.71760830239491</v>
+        <v>39.71700581534508</v>
       </c>
       <c r="K26" t="n">
-        <v>-104.9520888656285</v>
+        <v>-104.9529964927036</v>
       </c>
       <c r="L26" t="n">
-        <v>100.4</v>
+        <v>25.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Theft-other on Jul 20, 2026, 100 m from Cherry Creek Shopping Center (3030 E 1ST AVE). Victims: 1. Case #DP2026399148 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M233"/>
+  <dimension ref="A1:M328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16060,8 +16179,5613 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>20260725-2301-00</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>6900 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>35.14684118006692</v>
+      </c>
+      <c r="K234" t="n">
+        <v>-80.82544759809264</v>
+      </c>
+      <c r="L234" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>20260713-1954-00</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Extortion/Blackmail</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>300 SHARON TOWNSHIP LN</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>35.15734514344371</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-80.82395947870275</v>
+      </c>
+      <c r="L235" t="n">
+        <v>846.2</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Extortion/blackmail on Jul 13, 2026, 846 m from Southpark (300 SHARON TOWNSHIP LN). Status: Open. Case #20260713-1954-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>20260708-2322-01</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46211.16666666666</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Driving Under The Influence</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>90D</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>4000 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>35.15567429979806</v>
+      </c>
+      <c r="K236" t="n">
+        <v>-80.82377486075073</v>
+      </c>
+      <c r="L236" t="n">
+        <v>738.5</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 08, 2026, 738 m from Southpark (4000 SHARON RD). Status: Cleared by Arrest. Case #20260708-2322-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>20260725-1345-01</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>46227.16666666666</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K237" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L237" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 24, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1345-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>20260726-0712-02</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>23F</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>6300 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>35.15641923337007</v>
+      </c>
+      <c r="K238" t="n">
+        <v>-80.83429541207509</v>
+      </c>
+      <c r="L238" t="n">
+        <v>613</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>20260721-1118-01</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K239" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L239" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260721-1118-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>20260724-1414-04</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>6200 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>35.15078706372375</v>
+      </c>
+      <c r="K240" t="n">
+        <v>-80.8369057357377</v>
+      </c>
+      <c r="L240" t="n">
+        <v>599.6</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 13, 2026, 600 m from Southpark (6200 FAIRVIEW RD). Status: Open. Case #20260724-1414-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>20260703-2055-06</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K241" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L241" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 02, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260703-2055-06 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>20260703-0713-01</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K242" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L242" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 02, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260703-0713-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>20260717-0842-02</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Burglary/B&amp;E</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K243" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L243" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Burglary/b&amp;e on Jul 17, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260717-0842-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>20260722-1722-03</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>46222.16666666666</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>6600 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>35.14845720336839</v>
+      </c>
+      <c r="K244" t="n">
+        <v>-80.83089079594687</v>
+      </c>
+      <c r="L244" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 19, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260722-1722-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>20260707-1604-01</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>6100 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>35.15108488996929</v>
+      </c>
+      <c r="K245" t="n">
+        <v>-80.83828432277107</v>
+      </c>
+      <c r="L245" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 02, 2026, 718 m from Southpark (6100 FAIRVIEW RD). Status: Open. Case #20260707-1604-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>20260713-1143-00</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K246" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L246" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 13, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest by Another Agency. Case #20260713-1143-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>20260726-0550-00</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>23F</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>6700 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>35.1479657453291</v>
+      </c>
+      <c r="K247" t="n">
+        <v>-80.82922688152722</v>
+      </c>
+      <c r="L247" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>20260709-1333-01</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>6500 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>35.14920456105875</v>
+      </c>
+      <c r="K248" t="n">
+        <v>-80.83307576079913</v>
+      </c>
+      <c r="L248" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 09, 2026, 382 m from Southpark (6500 FAIRVIEW RD). Status: Open. Case #20260709-1333-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>20260725-0853-00</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>13A</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K249" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L249" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>20260714-1056-01</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K250" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L250" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 14, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260714-1056-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>20260720-1826-04</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K251" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L251" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 18, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260720-1826-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>20260722-1446-02</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K252" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L252" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 02, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260722-1446-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>20260720-2018-00</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>46223.16666666666</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>1800 ROXBOROUGH RD</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>35.15693620600955</v>
+      </c>
+      <c r="K253" t="n">
+        <v>-80.8291972833448</v>
+      </c>
+      <c r="L253" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 20, 2026, 573 m from Southpark (1800 ROXBOROUGH RD). Status: Open. Case #20260720-2018-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>20260722-2105-02</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Driving Under The Influence</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>90D</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L254" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 22, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260722-2105-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>20260713-1652-03</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Theft of Motor Vehicle Parts from Vehicle</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>23G</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>4300 BARCLAY DOWNS DR</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>35.1559228958258</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-80.83621502215044</v>
+      </c>
+      <c r="L255" t="n">
+        <v>689.7</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Theft of motor vehicle parts from vehicle on Jul 13, 2026, 690 m from Southpark (4300 BARCLAY DOWNS DR). Status: Open. Case #20260713-1652-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>20260718-1206-03</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L256" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260718-1206-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>20260710-0852-00</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Sudden/Natural Death Investigation</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>6000 PIEDMONT ROW DR S</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>35.14895379386067</v>
+      </c>
+      <c r="K257" t="n">
+        <v>-80.83963153088133</v>
+      </c>
+      <c r="L257" t="n">
+        <v>896.3</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Sudden/natural death investigation on Jul 09, 2026, 896 m from Southpark (6000 PIEDMONT ROW DR S). Status: Exceptionally Cleared. Case #20260710-0852-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>20260717-2031-00</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K258" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L258" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260717-2031-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>20260723-1057-02</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Wire Fraud</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>26E</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>6200 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>35.15078706372375</v>
+      </c>
+      <c r="K259" t="n">
+        <v>-80.8369057357377</v>
+      </c>
+      <c r="L259" t="n">
+        <v>599.6</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Wire fraud on Jul 22, 2026, 600 m from Southpark (6200 FAIRVIEW RD). Status: Open. Case #20260723-1057-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>20260705-1411-00</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>46206.16666666666</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K260" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L260" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 03, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260705-1411-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>20260711-1305-00</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>46213.16666666666</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K261" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L261" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260711-1305-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>20260724-0557-00</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Burglary/B&amp;E</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K262" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L262" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Burglary/b&amp;e on Jul 23, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260724-0557-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>20260713-1439-01</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>46215.16666666666</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L263" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 12, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260713-1439-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>20260719-1634-00</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Credit Card/Teller Fraud</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>26B</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>5500 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>35.15375121029781</v>
+      </c>
+      <c r="K264" t="n">
+        <v>-80.83607576012871</v>
+      </c>
+      <c r="L264" t="n">
+        <v>551.7</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Credit card/teller fraud on Jul 18, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260719-1634-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>20260717-2357-03</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>46219.16666666666</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Theft From Building</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>23D</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>4800 ASHLEY PARK LN</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>35.1479657453291</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-80.82922688152722</v>
+      </c>
+      <c r="L265" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 16, 2026, 450 m from Southpark (4800 ASHLEY PARK LN). Status: Open. Case #20260717-2357-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>20260722-2044-03</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>6100 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>35.15108488996929</v>
+      </c>
+      <c r="K266" t="n">
+        <v>-80.83828432277107</v>
+      </c>
+      <c r="L266" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 22, 2026, 718 m from Southpark (6100 FAIRVIEW RD). Status: Open. Case #20260722-2044-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>20260718-1425-00</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>4800 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>35.14644420018161</v>
+      </c>
+      <c r="K267" t="n">
+        <v>-80.83188614721075</v>
+      </c>
+      <c r="L267" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 18, 2026, 620 m from Southpark (4800 SHARON RD). Status: Open. Case #20260718-1425-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>20260718-1642-00</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>4800 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>35.14644420018161</v>
+      </c>
+      <c r="K268" t="n">
+        <v>-80.83188614721075</v>
+      </c>
+      <c r="L268" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 18, 2026, 620 m from Southpark (4800 SHARON RD). Status: Exceptionally Cleared. Case #20260718-1642-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>20260726-0657-00</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>23F</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>5500 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>35.15375121029781</v>
+      </c>
+      <c r="K269" t="n">
+        <v>-80.83607576012871</v>
+      </c>
+      <c r="L269" t="n">
+        <v>551.7</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>20260720-1107-04</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K270" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L270" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 14, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260720-1107-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>20260725-1348-05</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K271" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L271" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>20260729-1053-01</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>4500 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K272" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L272" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>20260706-0134-00</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>6500 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>35.14920456105875</v>
+      </c>
+      <c r="K273" t="n">
+        <v>-80.83307576079913</v>
+      </c>
+      <c r="L273" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 382 m from Southpark (6500 FAIRVIEW RD). Status: Open. Case #20260706-0134-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>20260727-1824-00</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J274" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K274" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L274" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>20260727-1945-02</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L275" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>20260709-0641-01</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>46211.16666666666</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J276" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L276" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 08, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260709-0641-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>20260722-0920-00</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>5300 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>35.14420159566059</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-80.83298000600156</v>
+      </c>
+      <c r="L277" t="n">
+        <v>885.4</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 885 m from Southpark (5300 SHARON RD). Status: Exceptionally Cleared. Case #20260722-0920-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>20260704-1737-00</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>46207.16666666666</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Credit Card/Teller Fraud</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>26B</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>6600 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>35.14845720336839</v>
+      </c>
+      <c r="K278" t="n">
+        <v>-80.83089079594687</v>
+      </c>
+      <c r="L278" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Credit card/teller fraud on Jul 04, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260704-1737-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>20260723-0938-05</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>46218.16666666666</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>13A</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>6600 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>35.14845720336839</v>
+      </c>
+      <c r="K279" t="n">
+        <v>-80.83089079594687</v>
+      </c>
+      <c r="L279" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 15, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260723-0938-05 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>20260714-2130-05</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K280" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L280" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 14, 2026, 179 m from Southpark (4400 SHARON RD). Status: Unfounded. Case #20260714-2130-05 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>20260722-1448-00</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>3900 COLONY RD</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>35.15489615849495</v>
+      </c>
+      <c r="K281" t="n">
+        <v>-80.82453042173836</v>
+      </c>
+      <c r="L281" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 22, 2026, 634 m from Southpark (3900 COLONY RD). Status: Unfounded. Case #20260722-1448-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>20260724-1649-01</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>46227.16666666666</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Peeping Tom</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>90H</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K282" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L282" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Peeping tom on Jul 24, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260724-1649-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>20260706-1114-01</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>4000 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>35.15567429979806</v>
+      </c>
+      <c r="K283" t="n">
+        <v>-80.82377486075073</v>
+      </c>
+      <c r="L283" t="n">
+        <v>738.5</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 738 m from Southpark (4000 SHARON RD). Status: Open. Case #20260706-1114-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>20260703-1606-03</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>46206.16666666666</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J284" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K284" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L284" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 03, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest. Case #20260703-1606-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>20260726-1824-01</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K285" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L285" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>20260706-1306-00</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J286" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L286" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260706-1306-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>20260710-1651-01</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>46213.16666666666</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J287" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K287" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L287" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260710-1651-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>20260721-1054-00</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Theft From Coin-Operated Machine Or Device</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>23E</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>6100 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>35.15108488996929</v>
+      </c>
+      <c r="K288" t="n">
+        <v>-80.83828432277107</v>
+      </c>
+      <c r="L288" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Theft from coin-operated machine or device on Jul 21, 2026, 718 m from Southpark (6100 FAIRVIEW RD). Status: Open. Case #20260721-1054-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>20260706-1754-00</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>6800 LOUISBURG SQUARE LN</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>35.14541141958989</v>
+      </c>
+      <c r="K289" t="n">
+        <v>-80.83239492414555</v>
+      </c>
+      <c r="L289" t="n">
+        <v>741.8</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 06, 2026, 742 m from Southpark (6800 LOUISBURG SQUARE LN). Status: Open. Case #20260706-1754-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>20260724-0616-01</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Burglary/B&amp;E</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L290" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Burglary/b&amp;e on Jul 23, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260724-0616-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>20260716-1025-00</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2200 REXFORD RD</t>
+        </is>
+      </c>
+      <c r="J291" t="n">
+        <v>35.15737066178394</v>
+      </c>
+      <c r="K291" t="n">
+        <v>-80.82972570752082</v>
+      </c>
+      <c r="L291" t="n">
+        <v>612.9</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 13, 2026, 613 m from Southpark (2200 REXFORD RD). Status: Open. Case #20260716-1025-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>20260707-0323-00</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>46210.16666666666</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J292" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K292" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L292" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 07, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260707-0323-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>20260728-1214-00</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>1800 ROXBOROUGH RD</t>
+        </is>
+      </c>
+      <c r="J293" t="n">
+        <v>35.15693620600955</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-80.8291972833448</v>
+      </c>
+      <c r="L293" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 17, 2026, 573 m from Southpark (1800 ROXBOROUGH RD). Status: Open. Case #20260728-1214-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>20260707-2104-01</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>46210.16666666666</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J294" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L294" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 07, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Exceptionally Cleared. Case #20260707-2104-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>20260709-2041-01</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L295" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 09, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260709-2041-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>20260712-2051-00</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>46215.16666666666</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>6700 PHILLIPS PLACE CT</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>35.14659329285514</v>
+      </c>
+      <c r="K296" t="n">
+        <v>-80.8278477116156</v>
+      </c>
+      <c r="L296" t="n">
+        <v>634.8</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 12, 2026, 635 m from Southpark (6700 PHILLIPS PLACE CT). Status: Open. Case #20260712-2051-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>20260718-2022-01</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L297" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest. Case #20260718-2022-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>20260728-1922-01</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J298" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K298" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L298" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>20260717-1828-00</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J299" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K299" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L299" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest. Case #20260717-1828-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>20260713-2148-07</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Damage/Vandalism Of Property</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J300" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K300" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L300" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Damage/vandalism of property on Jul 06, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260713-2148-07 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>20260717-1943-01</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K301" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L301" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260717-1943-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>20260728-1130-01</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J302" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K302" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L302" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>20260721-1528-01</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>6900 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J303" t="n">
+        <v>35.14684118006692</v>
+      </c>
+      <c r="K303" t="n">
+        <v>-80.82544759809264</v>
+      </c>
+      <c r="L303" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 21, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260721-1528-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>20260722-1544-00</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>4300 BARCLAY DOWNS DR</t>
+        </is>
+      </c>
+      <c r="J304" t="n">
+        <v>35.1559228958258</v>
+      </c>
+      <c r="K304" t="n">
+        <v>-80.83621502215044</v>
+      </c>
+      <c r="L304" t="n">
+        <v>689.7</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 21, 2026, 690 m from Southpark (4300 BARCLAY DOWNS DR). Status: Open. Case #20260722-1544-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>20260726-0952-00</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J305" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K305" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L305" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>20260714-1103-04</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Trespass Of Real Property</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>90J</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J306" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K306" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L306" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 14, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260714-1103-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>20260714-1049-03</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>8900 RACHEL FREEMAN WY</t>
+        </is>
+      </c>
+      <c r="J307" t="n">
+        <v>35.162796991439</v>
+      </c>
+      <c r="K307" t="n">
+        <v>-80.97457621910608</v>
+      </c>
+      <c r="L307" t="n">
+        <v>755.9</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 14, 2026, 756 m from Charlotte Premium Outlets (8900 RACHEL FREEMAN WY). Status: Open. Case #20260714-1049-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>20260723-0724-00</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Theft From Building</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>23D</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>9300 STEELE CREEK RD</t>
+        </is>
+      </c>
+      <c r="J308" t="n">
+        <v>35.16373788000934</v>
+      </c>
+      <c r="K308" t="n">
+        <v>-80.9686185584536</v>
+      </c>
+      <c r="L308" t="n">
+        <v>521.4</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 23, 2026, 521 m from Charlotte Premium Outlets (9300 STEELE CREEK RD). Status: Open. Case #20260723-0724-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>20260713-2349-01</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>9300 ROBERT IRWIN DR</t>
+        </is>
+      </c>
+      <c r="J309" t="n">
+        <v>35.16491450474356</v>
+      </c>
+      <c r="K309" t="n">
+        <v>-80.97095619384244</v>
+      </c>
+      <c r="L309" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 13, 2026, 396 m from Charlotte Premium Outlets (9300 ROBERT IRWIN DR). Status: Exceptionally Cleared. Case #20260713-2349-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>20260717-1629-01</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>5600 KELTONWOOD RD</t>
+        </is>
+      </c>
+      <c r="J310" t="n">
+        <v>35.16655081611235</v>
+      </c>
+      <c r="K310" t="n">
+        <v>-80.97476086867614</v>
+      </c>
+      <c r="L310" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 17, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260717-1629-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>20260725-1130-01</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J311" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K311" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L311" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 23, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260725-1130-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>20260721-1959-02</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Public Accident</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>13500 RIGSBY RD</t>
+        </is>
+      </c>
+      <c r="J312" t="n">
+        <v>35.16332668510686</v>
+      </c>
+      <c r="K312" t="n">
+        <v>-80.96669770382859</v>
+      </c>
+      <c r="L312" t="n">
+        <v>622.2</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Public accident on Jul 21, 2026, 622 m from Charlotte Premium Outlets (13500 RIGSBY RD). Status: Open. Case #20260721-1959-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>20260710-1339-00</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>5600 GARROW GLEN RD</t>
+        </is>
+      </c>
+      <c r="J313" t="n">
+        <v>35.16539493677813</v>
+      </c>
+      <c r="K313" t="n">
+        <v>-80.97704544416381</v>
+      </c>
+      <c r="L313" t="n">
+        <v>739.2</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 09, 2026, 739 m from Charlotte Premium Outlets (5600 GARROW GLEN RD). Status: Open. Case #20260710-1339-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>20260718-1639-02</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J314" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K314" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L314" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 18, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260718-1639-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>20260721-1652-01</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J315" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K315" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L315" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 21, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260721-1652-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>20260717-1504-02</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>46210.16666666666</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>4800 SHOPTON RD</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>35.17263853493539</v>
+      </c>
+      <c r="K316" t="n">
+        <v>-80.96174124648307</v>
+      </c>
+      <c r="L316" t="n">
+        <v>871.3</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 07, 2026, 871 m from Charlotte Premium Outlets (4800 SHOPTON RD). Status: Open. Case #20260717-1504-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>20260723-1659-01</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>5500 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>35.16919484075596</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-80.9710429684888</v>
+      </c>
+      <c r="L317" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 23, 2026, 151 m from Charlotte Premium Outlets (5500 NEW FASHION WY). Status: Open. Case #20260723-1659-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>20260721-1452-01</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L318" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260721-1452-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>20260725-1934-03</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>4900 TROJAN DR</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>35.16474336144204</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-80.96762879799847</v>
+      </c>
+      <c r="L319" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>20260722-2124-02</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>9400 STEELE CREEK RD</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>35.16250902126527</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-80.96982377170991</v>
+      </c>
+      <c r="L320" t="n">
+        <v>647.8</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 648 m from Charlotte Premium Outlets (9400 STEELE CREEK RD). Status: Open. Case #20260722-2124-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>20260729-1434-02</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Damage/Vandalism Of Property</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>5600 KELTONWOOD RD</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>35.16655081611235</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-80.97476086867614</v>
+      </c>
+      <c r="L321" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>20260715-1042-04</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Theft of Motor Vehicle Parts from Vehicle</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>23G</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>5600 KELTONWOOD RD</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>35.16655081611235</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-80.97476086867614</v>
+      </c>
+      <c r="L322" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Theft of motor vehicle parts from vehicle on Jul 13, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260715-1042-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>20260707-1238-01</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L323" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260707-1238-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>20260715-2015-02</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>46218.16666666666</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L324" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 15, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260715-2015-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>20260720-2155-00</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>46222.16666666666</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>4900 TROJAN DR</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>35.16474336144204</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-80.96762879799847</v>
+      </c>
+      <c r="L325" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 19, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260720-2155-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>20260721-1210-03</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>46219.16666666666</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>5500 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>35.16919484075596</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-80.9710429684888</v>
+      </c>
+      <c r="L326" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 16, 2026, 151 m from Charlotte Premium Outlets (5500 NEW FASHION WY). Status: Open. Case #20260721-1210-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>20260715-0940-02</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>46218.16666666666</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>9300 STEELE CREEK RD</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>35.16373788000934</v>
+      </c>
+      <c r="K327" t="n">
+        <v>-80.9686185584536</v>
+      </c>
+      <c r="L327" t="n">
+        <v>521.4</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 15, 2026, 521 m from Charlotte Premium Outlets (9300 STEELE CREEK RD). Status: Open. Case #20260715-0940-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>20260724-1333-02</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K328" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L328" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260724-1333-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M233"/>
+  <autoFilter ref="A1:M328"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16072,7 +21796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -16099,7 +21823,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:07:15.391218+00:00</t>
+          <t>2026-07-31 07:11:45.202134+00:00</t>
         </is>
       </c>
     </row>
@@ -16121,7 +21845,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:07:15.391218+00:00</t>
+          <t>2026-07-01 07:11:45.202134+00:00</t>
         </is>
       </c>
     </row>
@@ -16132,7 +21856,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>232</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
@@ -16142,7 +21866,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -16217,8 +21941,44 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>source:SOUTHPARK/CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OK fetched=73 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>source:CHARLOTTE/CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OK fetched=22 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>source:ABQUP/Albuquerque PD Incidents</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OK fetched=0 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-07-31/blotter_report.xlsx
+++ b/reports/2026-07-31/blotter_report.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$18</definedName>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="57" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,45 +473,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>nearest_m</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>most_recent</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>truncated</t>
         </is>
@@ -529,11 +535,13 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2200 Louisiana Boulevard Northeast Albuquerque NM 87110</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -547,9 +555,12 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="b">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -566,31 +577,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>5000 South Arizona Mills Circle Tempe AZ 85282</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>14.7</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>46232.21041666667</v>
       </c>
-      <c r="K3" t="b">
+      <c r="L3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -607,11 +623,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>8500 Beverly Boulevard, Los Angeles CA 90048</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -625,9 +643,12 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="b">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -644,31 +665,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>5404 New Fashion Way Charlotte NC 28278</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>443.5</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>46231.16666666666</v>
       </c>
-      <c r="K5" t="b">
+      <c r="L5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -685,31 +711,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>3000 East 1st Avenue, Denver CO 80206</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>144.7</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>46231.83333333334</v>
       </c>
-      <c r="K6" t="b">
+      <c r="L6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -726,31 +757,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>191.2</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="K7" s="3" t="n">
         <v>46232.0625</v>
       </c>
-      <c r="K7" t="b">
+      <c r="L7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -767,11 +803,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -785,9 +823,12 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="b">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -802,13 +843,15 @@
           <t>Lenox Square</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>NO COVERAGE</t>
         </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -822,9 +865,12 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="b">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -841,31 +887,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>145.2</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>46232.82986111111</v>
       </c>
-      <c r="K10" t="b">
+      <c r="L10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -882,31 +933,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>14</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>9</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>113.7</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="K11" s="3" t="n">
         <v>46231.92430555556</v>
       </c>
-      <c r="K11" t="b">
+      <c r="L11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -923,31 +979,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>13</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>9</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>178.9</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="K12" s="3" t="n">
         <v>46231.16666666666</v>
       </c>
-      <c r="K12" t="b">
+      <c r="L12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -962,13 +1023,15 @@
           <t>The Domain</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>NO COVERAGE</t>
         </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -982,9 +1045,12 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="b">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1001,36 +1067,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>7700 East Kellogg Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>17</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>8</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>288.9</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="K14" s="3" t="n">
         <v>46233.63055555556</v>
       </c>
-      <c r="K14" t="b">
+      <c r="L14" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7695,7 +7766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:22:12.812075+00:00</t>
+          <t>2026-07-31 07:28:37.517868+00:00</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7788,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 07:22:12.812075+00:00</t>
+          <t>2026-07-24 07:28:37.517868+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-31/blotter_report.xlsx
+++ b/reports/2026-07-31/blotter_report.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
+          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mill (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mill (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mill (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mill (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mill (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mill (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mill (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mill (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mill (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:28:37.517868+00:00</t>
+          <t>2026-07-31 07:31:55.362213+00:00</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 07:28:37.517868+00:00</t>
+          <t>2026-07-24 07:31:55.362213+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-31/blotter_report.xlsx
+++ b/reports/2026-07-31/blotter_report.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>14.7</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>145.2</v>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -954,13 +954,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>113.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46231.92430555556</v>
+        <v>46232.70902777778</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>178.9</v>
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
         <v>288.9</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46233.63055555556</v>
+        <v>46233.7625</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1487,443 +1487,435 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260449995_11</t>
+          <t>26C139724</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46227.69421296296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>BATTERY DV</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>211 211</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36.20300000011262</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K7" t="n">
-        <v>-86.69100000036219</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L7" t="n">
-        <v>113.7</v>
+        <v>1122.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20260451873_11</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36.20199999980591</v>
+        <v>47.70668788</v>
       </c>
       <c r="K8" t="n">
-        <v>-86.69299999962931</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L8" t="n">
-        <v>125.9</v>
+        <v>1145.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46231.00625</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>39.7162154712797</v>
+        <v>47.70668788</v>
       </c>
       <c r="K9" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L9" t="n">
-        <v>144.7</v>
+        <v>1145.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46230.75</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>39.7162154712797</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K10" t="n">
-        <v>-104.9512928115626</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L10" t="n">
-        <v>144.7</v>
+        <v>1251.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t xml:space="preserve">TE202674714         </t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46227.7375</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PROPERTY CRIME</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.7086028</v>
+        <v>33.37634047797651</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.324615154453</v>
+        <v>-111.9531278046354</v>
       </c>
       <c r="L11" t="n">
-        <v>145.2</v>
+        <v>1309.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46231.625</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PROPERTY CRIME</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47.7086028</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K12" t="n">
-        <v>-122.324615154453</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L12" t="n">
-        <v>145.2</v>
+        <v>1345.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>26C139922</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46227.5</v>
+        <v>46227.95277777778</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>7000 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.7086028</v>
+        <v>37.67195398477438</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.324615154453</v>
+        <v>-97.25533959083543</v>
       </c>
       <c r="L13" t="n">
-        <v>145.2</v>
+        <v>1383.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>20260449995_11</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46227.89583333334</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>SHOPLIFTING</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1933,56 +1925,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>211 211</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>39.71813319743836</v>
+        <v>36.20300000011262</v>
       </c>
       <c r="K14" t="n">
-        <v>-104.9522056316381</v>
+        <v>-86.69100000036219</v>
       </c>
       <c r="L14" t="n">
-        <v>148.6</v>
+        <v>113.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>20260451873_11</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.76041666666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>LOST PROPERTY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1992,56 +1984,56 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>433 433</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>35.15120046375475</v>
+        <v>36.20199999980591</v>
       </c>
       <c r="K15" t="n">
-        <v>-80.82867375349484</v>
+        <v>-86.69299999962931</v>
       </c>
       <c r="L15" t="n">
-        <v>178.9</v>
+        <v>125.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2051,56 +2043,56 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>35.15120046375475</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K16" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L16" t="n">
-        <v>178.9</v>
+        <v>144.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2110,52 +2102,52 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>35.15120046375475</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K17" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L17" t="n">
-        <v>178.9</v>
+        <v>144.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2169,52 +2161,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K18" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L18" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46231.625</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2228,56 +2220,56 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K19" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L19" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260727-1945-02</t>
+          <t>71842391876</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46227.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2287,26 +2279,26 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K20" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L20" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2328,15 +2320,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DP2026416370230300</t>
+          <t>DP2026408098239901</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>theft-bicycle</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2351,51 +2343,51 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>N MILWAUKEE ST / E 1ST AVE</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39.71666393731682</v>
+        <v>39.71813319743836</v>
       </c>
       <c r="K21" t="n">
-        <v>-104.9556403659223</v>
+        <v>-104.9522056316381</v>
       </c>
       <c r="L21" t="n">
-        <v>247.6</v>
+        <v>148.6</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DP2026415590230300</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.54236111111</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2405,56 +2397,56 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>39.71666393731682</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.9556403659223</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L22" t="n">
-        <v>247.6</v>
+        <v>178.9</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675399         </t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46229.9</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2462,54 +2454,58 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>33.38552975305072</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K23" t="n">
-        <v>-111.965328834686</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L23" t="n">
-        <v>262</v>
+        <v>178.9</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676101         </t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232.21041666667</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2517,54 +2513,58 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>33.38580430470485</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K24" t="n">
-        <v>-111.9660628528483</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L24" t="n">
-        <v>315.7</v>
+        <v>178.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71909585262</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2574,56 +2574,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.70858578</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.321918377919</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L25" t="n">
-        <v>338.4</v>
+        <v>178.9</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676030         </t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.83194444444</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2631,24 +2631,28 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>33.3805974892332</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K26" t="n">
-        <v>-111.9623154538272</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L26" t="n">
-        <v>361.4</v>
+        <v>178.9</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3566,30 +3570,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260452878_11</t>
+          <t>20260459134_11</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46229.60694444444</v>
+        <v>46232.70902777778</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>HARRASSMENT (NUISANCE)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3597,28 +3601,24 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2131 2131</t>
+          <t>TWO RIVERS PKWY</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>36.10599999977134</v>
+        <v>36.19000000021294</v>
       </c>
       <c r="K16" t="n">
-        <v>-86.8170000000033</v>
+        <v>-86.69000000027951</v>
       </c>
       <c r="L16" t="n">
-        <v>191.2</v>
+        <v>1455.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 191 m from The Mall at Green Hills (2131 2131). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260452878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Harrassment (nuisance) on Jul 29, 2026, 1456 m from Opry Mills (TWO RIVERS PKWY). Premises: PARK. Status: OPEN. Victims: 1. Case #20260459134 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3640,20 +3640,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260451477_11</t>
+          <t>20260452878_11</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46228.27083333334</v>
+        <v>46229.60694444444</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BURGLARY</t>
+          <t>POLICE INQUIRY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3663,21 +3663,21 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CHANNELKIRK LN</t>
+          <t>2131 2131</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>36.10999999969955</v>
+        <v>36.10599999977134</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.81000000032267</v>
+        <v>-86.8170000000033</v>
       </c>
       <c r="L17" t="n">
-        <v>630.5</v>
+        <v>191.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Burglary on Jul 25, 2026, 631 m from The Mall at Green Hills (CHANNELKIRK LN). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260451477 (use for a records request — full narratives are not published in open data).</t>
+          <t>Police inquiry on Jul 26, 2026, 191 m from The Mall at Green Hills (2131 2131). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260452878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3699,20 +3699,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260453759_11</t>
+          <t>20260451477_11</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46228.27083333334</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>BURGLARY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3722,21 +3722,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2024 2024</t>
+          <t>CHANNELKIRK LN</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>36.09999999975003</v>
+        <v>36.10999999969955</v>
       </c>
       <c r="K18" t="n">
-        <v>-86.81499999983789</v>
+        <v>-86.81000000032267</v>
       </c>
       <c r="L18" t="n">
-        <v>859.2</v>
+        <v>630.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 859 m from The Mall at Green Hills (2024 2024). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260453759 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary on Jul 25, 2026, 631 m from The Mall at Green Hills (CHANNELKIRK LN). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260451477 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3758,44 +3758,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260458322_11</t>
+          <t>20260453759_11</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232.0625</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BURGLARY - MOTOR VEHICLE</t>
+          <t>POLICE INQUIRY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Unarmed</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HILLSBORO PIKE</t>
+          <t>2024 2024</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>36.09999999975003</v>
       </c>
       <c r="K19" t="n">
-        <v>-86.82000000025143</v>
+        <v>-86.81499999983789</v>
       </c>
       <c r="L19" t="n">
-        <v>910.1</v>
+        <v>859.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Burglary - motor vehicle on Jul 29, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260458322 (use for a records request — full narratives are not published in open data).</t>
+          <t>Police inquiry on Jul 26, 2026, 859 m from The Mall at Green Hills (2024 2024). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260453759 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3817,25 +3817,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260450411_11</t>
+          <t>20260458322_11</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46228.02083333334</v>
+        <v>46232.0625</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SIMPLE ASSLT</t>
+          <t>BURGLARY - MOTOR VEHICLE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PERSONAL (HANDS)</t>
+          <t>Unarmed</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Simple asslt on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: PERSONAL (HANDS). Premises: HIGHWAY, ROAD, ALLEY. Status: OPEN. Victims: 1. Case #20260450411 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary - motor vehicle on Jul 29, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260458322 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3876,26 +3876,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20260450256_11</t>
+          <t>20260450411_11</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46228.02569444444</v>
+        <v>46228.02083333334</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- &gt;$1,000 BUT &lt; $2,500</t>
+          <t>SIMPLE ASSLT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PERSONAL (HANDS)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HILLSBORO</t>
+          <t>HILLSBORO PIKE</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3909,7 +3913,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft of merchandise- &gt;$1,000 but &lt; $2,500 on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260450256 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple asslt on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: PERSONAL (HANDS). Premises: HIGHWAY, ROAD, ALLEY. Status: OPEN. Victims: 1. Case #20260450411 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3931,15 +3935,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260449408_11</t>
+          <t>20260450256_11</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46227.61805555555</v>
+        <v>46228.02569444444</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>THEFT OF MERCHANDISE- &gt;$1,000 BUT &lt; $2,500</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3947,58 +3951,54 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2025 2025</t>
+          <t>HILLSBORO</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>36.11399999985069</v>
+        <v>36.09999999975003</v>
       </c>
       <c r="K22" t="n">
-        <v>-86.80900000023999</v>
+        <v>-86.82000000025143</v>
       </c>
       <c r="L22" t="n">
-        <v>969.2</v>
+        <v>910.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Lost property on Jul 24, 2026, 969 m from The Mall at Green Hills (2025 2025). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Case #20260449408 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft of merchandise- &gt;$1,000 but &lt; $2,500 on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260450256 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>GREENHILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>20260449408_11</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46227.61805555555</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>LOST PROPERTY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4008,26 +4008,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>2025 2025</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>47.7086028</v>
+        <v>36.11399999985069</v>
       </c>
       <c r="K23" t="n">
-        <v>-122.324615154453</v>
+        <v>-86.80900000023999</v>
       </c>
       <c r="L23" t="n">
-        <v>145.2</v>
+        <v>969.2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Lost property on Jul 24, 2026, 969 m from The Mall at Green Hills (2025 2025). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Case #20260449408 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4049,15 +4049,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71909585262</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4072,21 +4072,21 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>47.70858578</v>
+        <v>47.7086028</v>
       </c>
       <c r="K24" t="n">
-        <v>-122.321918377919</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L24" t="n">
-        <v>338.4</v>
+        <v>145.2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4108,15 +4108,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>71909585262</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.625</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4131,21 +4131,21 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.7086028</v>
+        <v>47.70858578</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.324615154453</v>
+        <v>-122.321918377919</v>
       </c>
       <c r="L25" t="n">
-        <v>145.2</v>
+        <v>338.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4167,44 +4167,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>71899643103</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46231.78263888889</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>116XX BLOCK OF AURORA AVE N</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>47.70504225</v>
+        <v>47.71354798</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.344834273165</v>
       </c>
       <c r="L26" t="n">
-        <v>938.8</v>
+        <v>1511</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 1511 m from Northgate Station (116XX BLOCK OF AURORA AVE N). Case #2026-221622 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4226,15 +4226,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>71896083189</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46228.875</v>
+        <v>46231.625</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4249,21 +4249,21 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NE 100TH ST / 5TH AVE NE</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>47.70132479</v>
+        <v>47.7086028</v>
       </c>
       <c r="K27" t="n">
-        <v>-122.3231272219471</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L27" t="n">
-        <v>785.6</v>
+        <v>145.2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4285,15 +4285,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>71890752645</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46227.5</v>
+        <v>46231.21458333333</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Destruction/Damage/Vandalism of Property</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4303,174 +4303,174 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>47.7086028</v>
+        <v>47.70668788</v>
       </c>
       <c r="K28" t="n">
-        <v>-122.324615154453</v>
+        <v>-122.311189989679</v>
       </c>
       <c r="L28" t="n">
-        <v>145.2</v>
+        <v>1145.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>Destruction/damage/vandalism of property on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220873 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>39.7162154712797</v>
+        <v>47.70668788</v>
       </c>
       <c r="K29" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L29" t="n">
-        <v>144.7</v>
+        <v>1145.7</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46231.00625</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>39.7162154712797</v>
+        <v>47.70668788</v>
       </c>
       <c r="K30" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L30" t="n">
-        <v>144.7</v>
+        <v>1145.7</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>71906728829</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46231</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>Theft of Motor Vehicle Parts or Accessories</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4480,174 +4480,174 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>9XX BLOCK OF N 103RD ST</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>39.71813319743836</v>
+        <v>47.70360675</v>
       </c>
       <c r="K31" t="n">
-        <v>-104.9522056316381</v>
+        <v>-122.346021623573</v>
       </c>
       <c r="L31" t="n">
-        <v>148.6</v>
+        <v>1551.2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft of motor vehicle parts or accessories on Jul 28, 2026, 1551 m from Northgate Station (9XX BLOCK OF N 103RD ST). Case #2026-222196 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DP2026416370230300</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>39.71666393731682</v>
+        <v>47.70504225</v>
       </c>
       <c r="K32" t="n">
-        <v>-104.9556403659223</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L32" t="n">
-        <v>247.6</v>
+        <v>938.8</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DP2026415590230300</t>
+          <t>71854915364</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46231.54236111111</v>
+        <v>46228.91527777778</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Not Reportable to NIBRS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>N 105TH ST / AURORA AVE N</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>39.71666393731682</v>
+        <v>47.70505121</v>
       </c>
       <c r="K33" t="n">
-        <v>-104.9556403659223</v>
+        <v>-122.3446941292056</v>
       </c>
       <c r="L33" t="n">
-        <v>247.6</v>
+        <v>1411</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Not reportable to nibrs on Jul 25, 2026, 1411 m from Northgate Station (N 105TH ST / AURORA AVE N). Case #2026-218646 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DP2026413635260700</t>
+          <t>71896083189</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46230.58125</v>
+        <v>46228.875</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4657,56 +4657,56 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2 N ADAMS ST</t>
+          <t>NE 100TH ST / 5TH AVE NE</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>39.71654731730718</v>
+        <v>47.70132479</v>
       </c>
       <c r="K34" t="n">
-        <v>-104.9482864243138</v>
+        <v>-122.3231272219471</v>
       </c>
       <c r="L34" t="n">
-        <v>384.1</v>
+        <v>785.6</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DP20266010142239900</t>
+          <t>71842391876</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46230.10416666666</v>
+        <v>46227.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>theft-other</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4716,26 +4716,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3444 E 2ND AVE</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>39.7193352135378</v>
+        <v>47.7086028</v>
       </c>
       <c r="K35" t="n">
-        <v>-104.9468354191938</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L35" t="n">
-        <v>576.2</v>
+        <v>145.2</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4757,44 +4757,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DP2026413301299900</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46229.95833333334</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>39.71957373655755</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K36" t="n">
-        <v>-104.9597628432634</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L36" t="n">
-        <v>670.6</v>
+        <v>144.7</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4816,44 +4816,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DP20266010143299900</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46229.9375</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>39.71957373655755</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K37" t="n">
-        <v>-104.9597628432634</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L37" t="n">
-        <v>670.6</v>
+        <v>144.7</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4875,44 +4875,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>DP2026408098239901</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>theft-bicycle</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>N MILWAUKEE ST / E 1ST AVE</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>39.71130989687384</v>
+        <v>39.71813319743836</v>
       </c>
       <c r="K38" t="n">
-        <v>-104.9490029653731</v>
+        <v>-104.9522056316381</v>
       </c>
       <c r="L38" t="n">
-        <v>696.3</v>
+        <v>148.6</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4934,15 +4934,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DP2026411500220400</t>
+          <t>DP2026416370230300</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46229.08333333334</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>burglary-residence-no-force</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4952,115 +4952,115 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>burglary</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>100 BLK N GARFIELD ST</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>39.71871773048673</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.9439679319565</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L39" t="n">
-        <v>779.5</v>
+        <v>247.6</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20260725-2301-00</t>
+          <t>DP2026415590230300</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46231.54236111111</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Other Unlisted Non-Criminal</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6900 FAIRVIEW RD</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>35.14684118006692</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K40" t="n">
-        <v>-80.82544759809264</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L40" t="n">
-        <v>722.6</v>
+        <v>247.6</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20260726-0712-02</t>
+          <t>DP2026413635260700</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46230.58125</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5070,56 +5070,56 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6300 CARNEGIE BV</t>
+          <t>2 N ADAMS ST</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>35.15641923337007</v>
+        <v>39.71654731730718</v>
       </c>
       <c r="K41" t="n">
-        <v>-80.83429541207509</v>
+        <v>-104.9482864243138</v>
       </c>
       <c r="L41" t="n">
-        <v>613</v>
+        <v>384.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20260726-0550-00</t>
+          <t>DP20266010142239900</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46230.10416666666</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>theft-other</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5129,233 +5129,233 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6700 FAIRVIEW RD</t>
+          <t>3444 E 2ND AVE</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>35.1479657453291</v>
+        <v>39.7193352135378</v>
       </c>
       <c r="K42" t="n">
-        <v>-80.82922688152722</v>
+        <v>-104.9468354191938</v>
       </c>
       <c r="L42" t="n">
-        <v>450.4</v>
+        <v>576.2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20260725-0853-00</t>
+          <t>DP2026413301299900</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.95833333334</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5700 CARNEGIE BV</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>35.15368289092867</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K43" t="n">
-        <v>-80.8398453262274</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L43" t="n">
-        <v>877.1</v>
+        <v>670.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20260726-0657-00</t>
+          <t>DP20266010143299900</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.9375</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5500 CARNEGIE BV</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>35.15375121029781</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K44" t="n">
-        <v>-80.83607576012871</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L44" t="n">
-        <v>551.7</v>
+        <v>670.6</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.1125</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K45" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L45" t="n">
-        <v>178.9</v>
+        <v>696.3</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>DP2026411500220400</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>burglary-residence-no-force</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5365,56 +5365,56 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>100 BLK N GARFIELD ST</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71871773048673</v>
       </c>
       <c r="K46" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9439679319565</v>
       </c>
       <c r="L46" t="n">
-        <v>178.9</v>
+        <v>779.5</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>DP2026409833230500</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46228.56944444445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-items-from-vehicle</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5424,26 +5424,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>theft-from-motor-vehicle</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>373 S JACKSON ST</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>35.15120046375475</v>
+        <v>39.70992379075913</v>
       </c>
       <c r="K47" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9426513848476</v>
       </c>
       <c r="L47" t="n">
-        <v>178.9</v>
+        <v>1159</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-items-from-vehicle on Jul 25, 2026, 1159 m from Cherry Creek Shopping Center (373 S JACKSON ST). Victims: 1. Case #DP2026409833 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260727-1945-02</t>
+          <t>20260725-2301-00</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -5473,36 +5473,36 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Other Unlisted Non-Criminal</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>899</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>6900 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>35.15120046375475</v>
+        <v>35.14684118006692</v>
       </c>
       <c r="K48" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.82544759809264</v>
       </c>
       <c r="L48" t="n">
-        <v>178.9</v>
+        <v>722.6</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260726-1824-01</t>
+          <t>20260726-0712-02</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -5532,36 +5532,36 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>All Other Offenses</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>90Z</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>6300 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>35.15120046375475</v>
+        <v>35.15641923337007</v>
       </c>
       <c r="K49" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.83429541207509</v>
       </c>
       <c r="L49" t="n">
-        <v>178.9</v>
+        <v>613</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5583,15 +5583,15 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>20260726-0550-00</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5601,26 +5601,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>6700 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>35.15120046375475</v>
+        <v>35.1479657453291</v>
       </c>
       <c r="K50" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.82922688152722</v>
       </c>
       <c r="L50" t="n">
-        <v>178.9</v>
+        <v>450.4</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5642,44 +5642,44 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>20260725-0853-00</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>5700 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>35.15120046375475</v>
+        <v>35.15368289092867</v>
       </c>
       <c r="K51" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.8398453262274</v>
       </c>
       <c r="L51" t="n">
-        <v>178.9</v>
+        <v>877.1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260726-0952-00</t>
+          <t>20260726-0657-00</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
@@ -5709,58 +5709,58 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>All Other Offenses</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>90Z</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>700 GOVERNOR MORRISON ST</t>
+          <t>5500 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>35.15648042297118</v>
+        <v>35.15375121029781</v>
       </c>
       <c r="K52" t="n">
-        <v>-80.82480681029648</v>
+        <v>-80.83607576012871</v>
       </c>
       <c r="L52" t="n">
-        <v>723.7</v>
+        <v>551.7</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260725-1934-03</t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5778,56 +5778,56 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4900 TROJAN DR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>35.16474336144204</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K53" t="n">
-        <v>-80.96762879799847</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L53" t="n">
-        <v>443.5</v>
+        <v>178.9</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260729-1434-02</t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Damage/Vandalism Of Property</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5837,56 +5837,56 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5600 KELTONWOOD RD</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>35.16655081611235</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K54" t="n">
-        <v>-80.97476086867614</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L54" t="n">
-        <v>496.6</v>
+        <v>178.9</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26C140260</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46228.77152777778</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5896,166 +5896,174 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K55" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L55" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>26C140486</t>
+          <t>20260727-1945-02</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46228.51944444444</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K56" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L56" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26C143336</t>
+          <t>20260726-1824-01</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TRESPASS</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MISC_OFFENSES</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K57" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L57" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26C520577</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46227.71388888889</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6065,56 +6073,56 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SUSP_CHARAC</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K58" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L58" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>26C520675</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46227.84236111111</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6124,56 +6132,56 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K59" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L59" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>26C142785</t>
+          <t>20260725-1137-00</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46231.96458333333</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EVADE POLICE</t>
+          <t>Suicide</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6183,56 +6191,56 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>DRIVING_VIO</t>
+          <t>801</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>E KELLOGG DR &amp; S ROCK RD</t>
+          <t>5600 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>37.67911842691625</v>
+        <v>35.15235596527605</v>
       </c>
       <c r="K60" t="n">
-        <v>-97.24451202953301</v>
+        <v>-80.84558404556884</v>
       </c>
       <c r="L60" t="n">
-        <v>473.3</v>
+        <v>1376.8</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suicide on Jul 25, 2026, 1377 m from Southpark (5600 FAIRVIEW RD). Status: Open. Case #20260725-1137-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26C141216</t>
+          <t>20260726-0952-00</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46229.90069444444</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CHECKED WELFARE OF A CHILD</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6242,115 +6250,115 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FAMILY</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>7300 BLOCK OF E KELLOGG ST</t>
+          <t>700 GOVERNOR MORRISON ST</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>37.67974587023429</v>
+        <v>35.15648042297118</v>
       </c>
       <c r="K61" t="n">
-        <v>-97.25225228651782</v>
+        <v>-80.82480681029648</v>
       </c>
       <c r="L61" t="n">
-        <v>537.4</v>
+        <v>723.7</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>26C141683</t>
+          <t>20260725-0631-00</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46230.58541666667</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MISC OFFICERS</t>
+          <t>Drug/Narcotic Violations</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>OUTSIDE_CASE</t>
+          <t>35A</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8100 BLOCK OF E KELLOGG ST</t>
+          <t>8300 STEELE CREEK RD</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>37.6797148529391</v>
+        <v>35.17291837763486</v>
       </c>
       <c r="K62" t="n">
-        <v>-97.24233946631864</v>
+        <v>-80.95939837774333</v>
       </c>
       <c r="L62" t="n">
-        <v>556.7</v>
+        <v>1070.3</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drug/narcotic violations on Jul 25, 2026, 1070 m from Charlotte Premium Outlets (8300 STEELE CREEK RD). Status: Open. Case #20260725-0631-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26C143446</t>
+          <t>20260725-1934-03</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6360,56 +6368,56 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4900 TROJAN DR</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>37.67911394923933</v>
+        <v>35.16474336144204</v>
       </c>
       <c r="K63" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.96762879799847</v>
       </c>
       <c r="L63" t="n">
-        <v>398.7</v>
+        <v>443.5</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>26C144013</t>
+          <t>20260729-1434-02</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46233.63055555556</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>Damage/Vandalism Of Property</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6419,26 +6427,26 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>290</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>5600 KELTONWOOD RD</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>37.67911394923933</v>
+        <v>35.16655081611235</v>
       </c>
       <c r="K64" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.97476086867614</v>
       </c>
       <c r="L64" t="n">
-        <v>398.7</v>
+        <v>496.6</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6460,44 +6468,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26C144067</t>
+          <t>26C139456</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>46232.71180555555</v>
+        <v>46227.42226851852</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+          <t>SUSPICIOUS CHARACTER BURGLARY UNIT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>TRAFFIC</t>
+          <t>SUSP_CHARAC</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8000 BLOCK OF E DOUGLAS AVE</t>
+          <t>7200 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>37.6865673723019</v>
+        <v>37.67196805016872</v>
       </c>
       <c r="K65" t="n">
-        <v>-97.24449812404205</v>
+        <v>-97.25239793155058</v>
       </c>
       <c r="L65" t="n">
-        <v>501</v>
+        <v>1271.2</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character burglary unit on Jul 24, 2026, 1271 m from Towne East Square (7200 BLOCK OF E LINCOLN ST). Case #26C139456 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6519,44 +6527,44 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26C143812</t>
+          <t>26C139724</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46232.88888888889</v>
+        <v>46227.69421296296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OTV-HIT AND RUN</t>
+          <t>BATTERY DV</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>OTHERTRAF_VIO</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>400 BLOCK OF S ROCK RD</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>37.68150034571348</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K66" t="n">
-        <v>-97.24450622724754</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L66" t="n">
-        <v>288.9</v>
+        <v>1122.4</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6578,19 +6586,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26C139706</t>
+          <t>26C140260</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>46227.66875</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
+        <v>46228.77152777778</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>LARCENY B SHOPLIFT</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>7700 BLOCK OF E KELLOGG ST</t>
@@ -6607,7 +6623,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6629,44 +6645,36 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>26C142387</t>
+          <t>26C140486</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46230.81597222222</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
-        </is>
-      </c>
+        <v>46228.51944444444</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>TRAFFIC</t>
-        </is>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>100 BLOCK OF S ROCK RD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>37.6865673723019</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K68" t="n">
-        <v>-97.24449812404205</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L68" t="n">
-        <v>501</v>
+        <v>398.7</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6688,44 +6696,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26C520282</t>
+          <t>26C143336</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>46231.625</v>
+        <v>46232.7125</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LOST MISC PROPERTY</t>
+          <t>TRESPASS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>LOST_PROPERTY</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7000 BLOCK OF E KELLOGG ST</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>37.67951495831583</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K69" t="n">
-        <v>-97.25782989544317</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L69" t="n">
-        <v>982.3</v>
+        <v>398.7</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
+          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6747,44 +6755,44 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>26C520741</t>
+          <t>26C143989</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46228.86111111111</v>
+        <v>46233.61180555556</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LARCENY B AUTO ACCESSORIES</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>700 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67384327067582</v>
       </c>
       <c r="K70" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.25634062142737</v>
       </c>
       <c r="L70" t="n">
-        <v>398.7</v>
+        <v>1259.5</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1260 m from Towne East Square (700 BLOCK OF S APACHE DR). Case #26C143989 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6806,459 +6814,487 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>26C520933</t>
+          <t>26C144045</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>46230.6125</v>
+        <v>46233.65833333333</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>DEAD BODIES FOUND NO WITNESS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>SUDDEN_DEATH</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>700 BLOCK OF S EASTRIDGE DR</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67625582907724</v>
       </c>
       <c r="K71" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.25926072916232</v>
       </c>
       <c r="L71" t="n">
-        <v>398.7</v>
+        <v>1264.7</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
+          <t>Dead bodies found no witness on Jul 30, 2026, 1265 m from Towne East Square (700 BLOCK OF S EASTRIDGE DR). Case #26C144045 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675652         </t>
+          <t>26C520577</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46230.77569444444</v>
+        <v>46227.71388888889</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
+          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SUSP_CHARAC</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>33.38314167531927</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K72" t="n">
-        <v>-111.9645674529712</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L72" t="n">
-        <v>14.7</v>
+        <v>398.7</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674996         </t>
+          <t>26C520675</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46228.65694444445</v>
+        <v>46227.84236111111</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>33.38314167531927</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K73" t="n">
-        <v>-111.9645674529712</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L73" t="n">
-        <v>14.7</v>
+        <v>398.7</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674783         </t>
+          <t>26C520776</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46227.91319444445</v>
+        <v>46229.45833333334</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>AUTO THEFT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>AUTOTHEFT</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>500 BLOCK OF N ROCK RD</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>33.38314167531927</v>
+        <v>37.6938385342284</v>
       </c>
       <c r="K74" t="n">
-        <v>-111.9645674529712</v>
+        <v>-97.24455420498546</v>
       </c>
       <c r="L74" t="n">
-        <v>14.7</v>
+        <v>1264</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+          <t>Auto theft on Jul 26, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520776 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675415         </t>
+          <t>26C139721</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46229.95</v>
+        <v>46227.625</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
+          <t>OTV-HIT AND RUN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>E LINCOLN ST &amp; S ROCK RD</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>33.38341075529574</v>
+        <v>37.67198361320128</v>
       </c>
       <c r="K75" t="n">
-        <v>-111.9652490281131</v>
+        <v>-97.24446143278816</v>
       </c>
       <c r="L75" t="n">
-        <v>68.59999999999999</v>
+        <v>1219.7</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
+          <t>Otv-hit and run on Jul 24, 2026, 1220 m from Towne East Square (E LINCOLN ST &amp; S ROCK RD). Case #26C139721 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675399         </t>
+          <t>26C139922</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46229.9</v>
+        <v>46227.95277777778</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7000 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>33.38552975305072</v>
+        <v>37.67195398477438</v>
       </c>
       <c r="K76" t="n">
-        <v>-111.965328834686</v>
+        <v>-97.25533959083543</v>
       </c>
       <c r="L76" t="n">
-        <v>262</v>
+        <v>1383.4</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676101         </t>
+          <t>26C140815</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46232.21041666667</v>
+        <v>46229.30625</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>900 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>33.38580430470485</v>
+        <v>37.67195267201163</v>
       </c>
       <c r="K77" t="n">
-        <v>-111.9660628528483</v>
+        <v>-97.25741761429009</v>
       </c>
       <c r="L77" t="n">
-        <v>315.7</v>
+        <v>1484.1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 26, 2026, 1484 m from Towne East Square (900 BLOCK OF S APACHE DR). Case #26C140815 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676030         </t>
+          <t>26C142785</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46231.83194444444</v>
+        <v>46231.96458333333</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>EVADE POLICE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>DRIVING_VIO</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>E KELLOGG DR &amp; S ROCK RD</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>33.3805974892332</v>
+        <v>37.67911842691625</v>
       </c>
       <c r="K78" t="n">
-        <v>-111.9623154538272</v>
+        <v>-97.24451202953301</v>
       </c>
       <c r="L78" t="n">
-        <v>361.4</v>
+        <v>473.3</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674893         </t>
+          <t>26C142917</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46228.35972222222</v>
+        <v>46232.18194444444</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
+          <t>WINDOWPEEPING</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7266,54 +7302,58 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>SEX_OFFENSES1</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4XXX S WENDLER DR</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>33.38130369903515</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K79" t="n">
-        <v>-111.9695754725762</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L79" t="n">
-        <v>517</v>
+        <v>1285.1</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
+          <t>Windowpeeping on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C142917 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675649         </t>
+          <t>26C141216</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>46230.76944444444</v>
+        <v>46229.90069444444</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
+          <t>CHECKED WELFARE OF A CHILD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7321,56 +7361,56 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>FAMILY</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4XXX S DARROW DR</t>
+          <t>7300 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>33.38128291577831</v>
+        <v>37.67974587023429</v>
       </c>
       <c r="K80" t="n">
-        <v>-111.9593051545489</v>
+        <v>-97.25225228651782</v>
       </c>
       <c r="L80" t="n">
-        <v>533.1</v>
+        <v>537.4</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
+          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674654         </t>
+          <t>26C143148</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46227.62708333333</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] ACCIDENT - HIT AND RUN                                                   </t>
-        </is>
-      </c>
+        <v>46232.52430555555</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>OTHER</t>
@@ -7379,106 +7419,110 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>BASELINE RD / S DARROW DR</t>
+          <t>900 BLOCK OF S ENOCH DR</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>33.37825351544224</v>
+        <v>37.67197658912259</v>
       </c>
       <c r="K81" t="n">
-        <v>-111.9611381808533</v>
+        <v>-97.2456018407935</v>
       </c>
       <c r="L81" t="n">
-        <v>640.6</v>
+        <v>1203</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 29, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C143148 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675235         </t>
+          <t>26C141683</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>46229.31597222222</v>
+        <v>46230.58541666667</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
+          <t>MISC OFFICERS</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>OUTSIDE_CASE</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>BASELINE RD / I10</t>
+          <t>8100 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>33.37824262058852</v>
+        <v>37.6797148529391</v>
       </c>
       <c r="K82" t="n">
-        <v>-111.9680044627475</v>
+        <v>-97.24233946631864</v>
       </c>
       <c r="L82" t="n">
-        <v>645.4</v>
+        <v>556.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675001         </t>
+          <t>26C143446</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>46228.66944444444</v>
+        <v>46232.7125</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7486,249 +7530,2918 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1XXX W BASELINE RD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>33.377865729326</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K83" t="n">
-        <v>-111.9618554026273</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L83" t="n">
-        <v>650.2</v>
+        <v>398.7</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676035         </t>
+          <t>26C144013</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46231.85555555556</v>
+        <v>46233.63055555556</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1XXX W LA JOLLA DR</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>33.38909587497265</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K84" t="n">
-        <v>-111.961540133513</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L84" t="n">
-        <v>704.8</v>
+        <v>398.7</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675946         </t>
+          <t>26C144067</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46231.63888888889</v>
+        <v>46232.71180555555</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TRAFFIC</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1XXX W BASELINE RD</t>
+          <t>8000 BLOCK OF E DOUGLAS AVE</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>33.37795738260824</v>
+        <v>37.6865673723019</v>
       </c>
       <c r="K85" t="n">
-        <v>-111.959149564986</v>
+        <v>-97.24449812404205</v>
       </c>
       <c r="L85" t="n">
-        <v>773.7</v>
+        <v>501</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
+          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674935         </t>
+          <t>26C142294</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>46228.47222222222</v>
+        <v>46231.42847222222</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
+          <t>FOUND MISC PROPERTY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>FOUND_PROP</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1XXX W BASELINE RD</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>33.37594547787401</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K86" t="n">
-        <v>-111.9593287567214</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L86" t="n">
-        <v>946.9</v>
+        <v>1251.5</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
+          <t>Found misc property on Jul 28, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142294 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>26C144131</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>E BAYLEY ST &amp; S GOVERNEOUR RD</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>37.67014134415807</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-97.25360392908074</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1498.8</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 30, 2026, 1499 m from Towne East Square (E BAYLEY ST &amp; S GOVERNEOUR RD). Case #26C144131 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>26C143812</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46232.88888888889</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>OTV-HIT AND RUN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>400 BLOCK OF S ROCK RD</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>37.68150034571348</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-97.24450622724754</v>
+      </c>
+      <c r="L88" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>26C139586</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46227.55138888889</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>600 BLOCK OF S EASTERN AVE</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>37.6774046653855</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-97.23656061094495</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139586 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>26C144101</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46233.72152777778</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>600 BLOCK OF S APACHE DR</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>37.67516836949827</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-97.25367616461408</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 30, 2026, 1002 m from Towne East Square (600 BLOCK OF S APACHE DR). Case #26C144101 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>26C139706</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46227.66875</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>37.67911394923933</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-97.24743308095542</v>
+      </c>
+      <c r="L91" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>26C141863</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46230.75486111111</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>RUNAWAY</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>MISC_OFFENSES</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S HUNTER ST</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>37.67688443377517</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-97.26003808987583</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1285.1</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Runaway on Jul 27, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C141863 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>26C142249</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46230.75</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BATTERY ABW</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S MISSION RD</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>37.6756469679485</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-97.25850032865422</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1251.5</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>26C142387</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46230.81597222222</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TRAFFIC</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>100 BLOCK OF S ROCK RD</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>37.6865673723019</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-97.24449812404205</v>
+      </c>
+      <c r="L94" t="n">
+        <v>501</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>26C142657</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46231.79166666666</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>INTERFERENCE W PARENTAL CUSTODY</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>MISC_OFFENSES</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>900 BLOCK OF S ENOCH DR</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>37.67197658912259</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-97.2456018407935</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1203</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Interference w parental custody on Jul 28, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C142657 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>26C142768</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46231.94305555556</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CHECKED WELFARE OF A CHILD</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>FAMILY</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>6500 BLOCK OF E MORRIS ST</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>37.67377815761698</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-97.2605034310844</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1519.9</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Checked welfare of a child on Jul 28, 2026, 1520 m from Towne East Square (6500 BLOCK OF E MORRIS ST). Case #26C142768 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>26C143218</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46232.58333333334</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DISTURB THE PEACE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DISORDERLY</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S HUNTER ST</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>37.67688443377517</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-97.26003808987583</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1285.1</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Disturb the peace on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C143218 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>26C143562</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46232.93958333333</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MENTAL CASES</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>MENTAL_CASE</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>600 BLOCK OF S EASTERN AVE</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>37.6774046653855</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-97.23656061094495</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Mental cases on Jul 29, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C143562 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>26C143576</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46232.96111111111</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7500 BLOCK OF E LINCOLN ST</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>37.67197300274878</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-97.24902708647107</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1201.1</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 29, 2026, 1201 m from Towne East Square (7500 BLOCK OF E LINCOLN ST). Case #26C143576 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>26C143936</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46233.55972222222</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>POSSESSION OF PARAPHERNALIA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>DRUGS</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>500 BLOCK OF S HUNTER ST</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>37.67912059117884</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-97.25894321098265</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1089.5</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Possession of paraphernalia on Jul 30, 2026, 1090 m from Towne East Square (500 BLOCK OF S HUNTER ST). Case #26C143936 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>26C520567</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46227.6875</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>LARCENY B FROM AUTO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>7200 BLOCK OF E BAYLEY ST</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>37.67101904846645</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-97.25239274309988</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1370.6</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Larceny b from auto on Jul 24, 2026, 1371 m from Towne East Square (7200 BLOCK OF E BAYLEY ST). Case #26C520567 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>26C520979</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>46231.94583333333</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SUSPICIOUS CHARACTER SIB UNIT</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>SUSP_CHARAC</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>500 BLOCK OF N ROCK RD</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>37.6938385342284</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-97.24455420498546</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1264</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Suspicious character sib unit on Jul 28, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520979 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>26C520282</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>46231.625</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>LOST MISC PROPERTY</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>LOST_PROPERTY</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>7000 BLOCK OF E KELLOGG ST</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>37.67951495831583</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-97.25782989544317</v>
+      </c>
+      <c r="L103" t="n">
+        <v>982.3</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>26C520741</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46228.86111111111</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>LARCENY B AUTO ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>37.67911394923933</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-97.24743308095542</v>
+      </c>
+      <c r="L104" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>26C520933</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>46230.6125</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>LARCENY B SHOPLIFT</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>37.67911394923933</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-97.24743308095542</v>
+      </c>
+      <c r="L105" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>26C521105</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>46233.075</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>REVOCATION SUSP DL</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S WOODLAWN BLVD</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>37.67556302964613</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-97.26215557703324</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1520.5</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Revocation susp dl on Jul 30, 2026, 1520 m from Towne East Square (700 BLOCK OF S WOODLAWN BLVD). Case #26C521105 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>ARZMILLS</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Arizona Mills</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675652         </t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>46230.77569444444</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>33.38314167531927</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-111.9645674529712</v>
+      </c>
+      <c r="L107" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674996         </t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>46228.65694444445</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>33.38314167531927</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-111.9645674529712</v>
+      </c>
+      <c r="L108" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674783         </t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>46227.91319444445</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>33.38314167531927</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-111.9645674529712</v>
+      </c>
+      <c r="L109" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675415         </t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>46229.95</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>33.38341075529574</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-111.9652490281131</v>
+      </c>
+      <c r="L110" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675399         </t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>46229.9</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>33.38552975305072</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-111.965328834686</v>
+      </c>
+      <c r="L111" t="n">
+        <v>262</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676101         </t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>46232.21041666667</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>33.38580430470485</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-111.9660628528483</v>
+      </c>
+      <c r="L112" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676030         </t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>46231.83194444444</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>33.3805974892332</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-111.9623154538272</v>
+      </c>
+      <c r="L113" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674893         </t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>46228.35972222222</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4XXX S WENDLER DR</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>33.38130369903515</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-111.9695754725762</v>
+      </c>
+      <c r="L114" t="n">
+        <v>517</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675649         </t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>46230.76944444444</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>4XXX S DARROW DR</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>33.38128291577831</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-111.9593051545489</v>
+      </c>
+      <c r="L115" t="n">
+        <v>533.1</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674654         </t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>46227.62708333333</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[GO-0] ACCIDENT - HIT AND RUN                                                   </t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>BASELINE RD / S DARROW DR</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>33.37825351544224</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-111.9611381808533</v>
+      </c>
+      <c r="L116" t="n">
+        <v>640.6</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675235         </t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>46229.31597222222</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>BASELINE RD / I10</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>33.37824262058852</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-111.9680044627475</v>
+      </c>
+      <c r="L117" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675001         </t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>46228.66944444444</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1XXX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>33.377865729326</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-111.9618554026273</v>
+      </c>
+      <c r="L118" t="n">
+        <v>650.2</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676035         </t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>46231.85555555556</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1XXX W LA JOLLA DR</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>33.38909587497265</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-111.961540133513</v>
+      </c>
+      <c r="L119" t="n">
+        <v>704.8</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675946         </t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>46231.63888888889</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1XXX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>33.37795738260824</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-111.959149564986</v>
+      </c>
+      <c r="L120" t="n">
+        <v>773.7</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674935         </t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>46228.47222222222</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1XXX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>33.37594547787401</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-111.9593287567214</v>
+      </c>
+      <c r="L121" t="n">
+        <v>946.9</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t xml:space="preserve">TE202674869         </t>
         </is>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E122" s="3" t="n">
         <v>46228.26388888889</v>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t xml:space="preserve">[SC-0] LOST - PROPERTY (NON-FIREARM, OTHER THAN GOV'T ISSUED ID)                </t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
         <is>
           <t>PARKSIDE DR / W FREMONT DR</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J122" t="n">
         <v>33.38169955020192</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K122" t="n">
         <v>-111.954283203492</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L122" t="n">
         <v>967.3</v>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674568         </t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>46227.44722222222</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>9XX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>33.37784058487316</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-111.9548908569819</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1079.6</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 24, 2026, 1080 m from Arizona Mills (9XX W BASELINE RD). Case #TE202674568          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE2026601259        </t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>46229.58055555556</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[0] CRIMINAL DAMAGE - UNDER $1000                                               </t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1XXX W SOUTHERN AVE</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>33.39259581629993</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-111.9580558007179</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1198.6</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>[0] criminal damage - under $1000 on Jul 26, 2026, 1199 m from Arizona Mills (1XXX W SOUTHERN AVE). Case #TE2026601259         (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676006         </t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>46231.77708333333</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[GO-0] DEATH                                                                    </t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2XXX W SOUTHERN AVE</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>33.38855944643347</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-111.9758211943486</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1202.1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>[go-0] death on Jul 28, 2026, 1202 m from Arizona Mills (2XXX W SOUTHERN AVE). Case #TE202676006          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674741         </t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>46227.81666666667</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>33.37634047797651</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-111.9531278046354</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1309.4</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674741          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674557         </t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>46227.4125</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] WARNING - DISORDERLY CONDUCT                                             </t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>33.37634047797651</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-111.9531278046354</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1309.4</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>[sc-0] warning - disorderly conduct on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674557          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674714         </t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>46227.7375</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>33.37634047797651</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-111.9531278046354</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1309.4</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675136         </t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>46228.97847222222</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>33.3757495513233</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-111.9531832468173</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1345.1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676025         </t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>46231.82430555556</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] WARRANT - BOOKED INTO DETENTION                                          </t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>7XXX S 48TH ST</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>33.38154948911996</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-111.9788828064167</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1346.3</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>[sc-0] warrant - booked into detention on Jul 28, 2026, 1346 m from Arizona Mills (7XXX S 48TH ST). Case #TE202676025          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674804         </t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>46227.98263888889</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>MCKEMY ST / S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>33.37562594922362</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-111.9529211309643</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1372.7</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>[240] motor vehicle theft on Jul 24, 2026, 1373 m from Arizona Mills (MCKEMY ST / S HARDY DR). Case #TE202674804          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675422         </t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>46229.96111111111</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3XXX S 52ND ST</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>33.3959248712565</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-111.9704886613678</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1512</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>[sc-0] info - information other (non-criminal) on Jul 26, 2026, 1512 m from Arizona Mills (3XXX S 52ND ST). Case #TE202675422          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674830         </t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>46228.05902777778</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>SOUTHERN AVE / S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>33.39284504948579</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-111.9519846600515</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1578</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Incident on Jul 25, 2026, 1578 m from Arizona Mills (SOUTHERN AVE / S HARDY DR). Case #TE202674830          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675096         </t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>46228.88680555556</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[11D] MOLESTATION OF A CHILD                                                    </t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>7XX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>33.37881261615141</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-111.9483590935493</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1581.2</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>[11d] molestation of a child on Jul 25, 2026, 1581 m from Arizona Mills (7XX W BASELINE RD). Case #TE202675096          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M87"/>
+  <autoFilter ref="A1:M134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7739,7 +10452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -7766,7 +10479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:31:55.362213+00:00</t>
+          <t>2026-07-31 07:34:21.761817+00:00</t>
         </is>
       </c>
     </row>
@@ -7783,147 +10496,145 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cutoff</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:31:55.362213+00:00</t>
-        </is>
+          <t>radius_m</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>total_incidents</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>86</v>
+          <t>cutoff</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:34:21.761817+00:00</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>violent_incidents</t>
+          <t>total_incidents</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coverage_gaps</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LENOX, THEDOMAIN</t>
-        </is>
+          <t>violent_incidents</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>source:BEVCENTER/LAPD NIBRS Offenses 2026-present</t>
+          <t>coverage_gaps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OK fetched=0 truncated=False</t>
+          <t>LENOX, THEDOMAIN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>source:OPRYMILLS/Metro Nashville PD Incidents</t>
+          <t>source:BEVCENTER/LAPD NIBRS Offenses 2026-present</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OK fetched=14 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>source:GREENHILLS/Metro Nashville PD Incidents</t>
+          <t>source:OPRYMILLS/Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OK fetched=9 truncated=False</t>
+          <t>OK fetched=15 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>source:NORTHGATE/Seattle PD Crime Data</t>
+          <t>source:GREENHILLS/Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OK fetched=6 truncated=False</t>
+          <t>OK fetched=9 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>source:CHERRYCREEK/Denver PD Crime</t>
+          <t>source:NORTHGATE/Seattle PD Crime Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OK fetched=11 truncated=False</t>
+          <t>OK fetched=12 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source:SOUTHPARK/CMPD Incidents</t>
+          <t>source:CHERRYCREEK/Denver PD Crime</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OK fetched=13 truncated=False</t>
+          <t>OK fetched=12 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>source:CHARLOTTE/CMPD Incidents</t>
+          <t>source:SOUTHPARK/CMPD Incidents</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OK fetched=2 truncated=False</t>
+          <t>OK fetched=14 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>source:ABQUP/Albuquerque PD Incidents</t>
+          <t>source:CHARLOTTE/CMPD Incidents</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OK fetched=0 truncated=False</t>
+          <t>OK fetched=3 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>source:INTLPLAZA/Tampa PD Crimes (365d)</t>
+          <t>source:ABQUP/Albuquerque PD Incidents</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7935,29 +10646,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>source:TOWNEEAST/Wichita PD Crimes (90d)</t>
+          <t>source:INTLPLAZA/Tampa PD Crimes (365d)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OK fetched=38 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>source:TOWNEEAST/Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OK fetched=93 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>source:ARZMILLS/Tempe PD General Offenses</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>OK fetched=16 truncated=False</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OK fetched=28 truncated=False</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B18"/>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-07-31/blotter_report.xlsx
+++ b/reports/2026-07-31/blotter_report.xlsx
@@ -10479,7 +10479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:34:21.761817+00:00</t>
+          <t>2026-07-31 07:36:57.686613+00:00</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 07:34:21.761817+00:00</t>
+          <t>2026-07-24 07:36:57.686613+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-31/blotter_report.xlsx
+++ b/reports/2026-07-31/blotter_report.xlsx
@@ -10479,7 +10479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:36:57.686613+00:00</t>
+          <t>2026-07-31 07:45:48.319120+00:00</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 07:36:57.686613+00:00</t>
+          <t>2026-07-24 07:45:48.319120+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-31/blotter_report.xlsx
+++ b/reports/2026-07-31/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,16 +595,16 @@
         <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
         <v>14.7</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>46232.21041666667</v>
+        <v>46233.33055555556</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
@@ -766,26 +766,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>46232.0625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="b">
         <v>0</v>
       </c>
@@ -812,13 +808,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -826,8 +822,12 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -942,26 +942,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>46232.70902777778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
         <v>0</v>
       </c>
@@ -1076,19 +1072,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
         <v>288.9</v>
@@ -1117,7 +1113,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -1892,30 +1888,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260449995_11</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1925,56 +1921,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>211 211</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36.20300000011262</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K14" t="n">
-        <v>-86.69100000036219</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L14" t="n">
-        <v>113.7</v>
+        <v>144.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260451873_11</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1984,56 +1980,56 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36.20199999980591</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.69299999962931</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L15" t="n">
-        <v>125.9</v>
+        <v>144.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2043,56 +2039,56 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>39.7162154712797</v>
+        <v>47.7086028</v>
       </c>
       <c r="K16" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L16" t="n">
-        <v>144.7</v>
+        <v>145.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46231.625</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2102,52 +2098,52 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.7162154712797</v>
+        <v>47.7086028</v>
       </c>
       <c r="K17" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L17" t="n">
-        <v>144.7</v>
+        <v>145.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2161,52 +2157,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L18" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46231.625</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2220,56 +2216,56 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K19" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L19" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46227.5</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2279,56 +2275,56 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K20" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L20" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2338,26 +2334,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39.71813319743836</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K21" t="n">
-        <v>-104.9522056316381</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L21" t="n">
-        <v>148.6</v>
+        <v>178.9</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2379,11 +2375,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2416,7 +2412,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2438,11 +2434,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>20260727-1945-02</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2475,37 +2471,37 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>DP2026416370230300</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2515,56 +2511,56 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K24" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L24" t="n">
-        <v>178.9</v>
+        <v>247.6</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>DP2026415590230300</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46231.54236111111</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2574,56 +2570,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K25" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L25" t="n">
-        <v>178.9</v>
+        <v>247.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t xml:space="preserve">TE202675399         </t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2631,28 +2627,24 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>23C</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35.15120046375475</v>
+        <v>33.38552975305072</v>
       </c>
       <c r="K26" t="n">
-        <v>-80.82867375349484</v>
+        <v>-111.965328834686</v>
       </c>
       <c r="L26" t="n">
-        <v>178.9</v>
+        <v>262</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2668,18 +2660,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -2756,30 +2748,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260449995_11</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2789,56 +2781,56 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>211 211</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36.20300000011262</v>
+        <v>47.7086028</v>
       </c>
       <c r="K2" t="n">
-        <v>-86.69100000036219</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L2" t="n">
-        <v>113.7</v>
+        <v>145.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260451873_11</t>
+          <t>71909585262</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2848,115 +2840,115 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>36.20199999980591</v>
+        <v>47.70858578</v>
       </c>
       <c r="K3" t="n">
-        <v>-86.69299999962931</v>
+        <v>-122.321918377919</v>
       </c>
       <c r="L3" t="n">
-        <v>125.9</v>
+        <v>338.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20260451698_11</t>
+          <t>71899643103</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46228.89097222222</v>
+        <v>46231.78263888889</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>POSSESSION OF A CONTROLLED SUBSTANCE</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>116XX BLOCK OF AURORA AVE N</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36.20199999980591</v>
+        <v>47.71354798</v>
       </c>
       <c r="K4" t="n">
-        <v>-86.69299999962931</v>
+        <v>-122.344834273165</v>
       </c>
       <c r="L4" t="n">
-        <v>125.9</v>
+        <v>1511</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Possession of a controlled substance on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260451698 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 1511 m from Northgate Station (116XX BLOCK OF AURORA AVE N). Case #2026-221622 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20260457817_11</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46231.92430555556</v>
+        <v>46231.625</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- $1,000 OR LESS</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2966,233 +2958,233 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>36.20000000001247</v>
+        <v>47.7086028</v>
       </c>
       <c r="K5" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L5" t="n">
-        <v>387.3</v>
+        <v>145.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Theft of merchandise- $1,000 or less on Jul 28, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260457817 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20260451780_11</t>
+          <t>71890752645</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46231.21458333333</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LARC - FROM BLDG</t>
+          <t>Destruction/Damage/Vandalism of Property</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OPRY MILLS</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36.20000000001247</v>
+        <v>47.70668788</v>
       </c>
       <c r="K6" t="n">
-        <v>-86.70000000020825</v>
+        <v>-122.311189989679</v>
       </c>
       <c r="L6" t="n">
-        <v>768.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Larc - from bldg on Jul 25, 2026, 768 m from Opry Mills (OPRY MILLS). Premises: RESTAURANT. Status: OPEN. Victims: 1. Case #20260451780 (use for a records request — full narratives are not published in open data).</t>
+          <t>Destruction/damage/vandalism of property on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220873 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260451462_11</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46228.6875</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70668788</v>
       </c>
       <c r="K7" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L7" t="n">
-        <v>808.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260451462 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20260455357_11</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.79166666666</v>
+        <v>46231.00625</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70668788</v>
       </c>
       <c r="K8" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L8" t="n">
-        <v>808.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 27, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: DEPARTMENT, DISCOUNT STORE. Status: OPEN. Victims: 1. Case #20260455357 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260457791_11</t>
+          <t>71906728829</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46231.9</v>
+        <v>46231</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- $1,000 OR LESS</t>
+          <t>Theft of Motor Vehicle Parts or Accessories</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3202,174 +3194,174 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>9XX BLOCK OF N 103RD ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70360675</v>
       </c>
       <c r="K9" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.346021623573</v>
       </c>
       <c r="L9" t="n">
-        <v>808.3</v>
+        <v>1551.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Theft of merchandise- $1,000 or less on Jul 28, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260457791 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft of motor vehicle parts or accessories on Jul 28, 2026, 1551 m from Northgate Station (9XX BLOCK OF N 103RD ST). Case #2026-222196 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20260456995_11</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46227.68333333333</v>
+        <v>46230.4375</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FRAUD -  ILLEG USE OF CREDIT CARDS</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70504225</v>
       </c>
       <c r="K10" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L10" t="n">
-        <v>808.3</v>
+        <v>938.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Fraud -  illeg use of credit cards on Jul 24, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: RESTAURANT. Status: OPEN. Victims: 1. Case #20260456995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20260456990_11</t>
+          <t>71854915364</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46227.68333333333</v>
+        <v>46228.91527777778</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FRAUD -  ILLEG USE OF CREDIT CARDS</t>
+          <t>Not Reportable to NIBRS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>N 105TH ST / AURORA AVE N</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70505121</v>
       </c>
       <c r="K11" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.3446941292056</v>
       </c>
       <c r="L11" t="n">
-        <v>808.3</v>
+        <v>1411</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Fraud -  illeg use of credit cards on Jul 24, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260456990 (use for a records request — full narratives are not published in open data).</t>
+          <t>Not reportable to nibrs on Jul 25, 2026, 1411 m from Northgate Station (N 105TH ST / AURORA AVE N). Case #2026-218646 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20260456993_11</t>
+          <t>71896083189</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46227.68333333333</v>
+        <v>46228.875</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FRAUD -  ILLEG USE OF CREDIT CARDS</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3379,335 +3371,351 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>NE 100TH ST / 5TH AVE NE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70132479</v>
       </c>
       <c r="K12" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.3231272219471</v>
       </c>
       <c r="L12" t="n">
-        <v>808.3</v>
+        <v>785.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Fraud -  illeg use of credit cards on Jul 24, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260456993 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20260453969_11</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.16666666666</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>white-collar-crime</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OPRYLAND DR</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>36.20999999970633</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K13" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L13" t="n">
-        <v>808.3</v>
+        <v>144.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 27, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260453969 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260453969_12</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46230.16666666666</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>larceny</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OPRYLAND DR</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36.20999999970633</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K14" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L14" t="n">
-        <v>808.3</v>
+        <v>144.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 27, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 2. Case #20260453969 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260453969_13</t>
+          <t>DP2026416370230300</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46230.16666666666</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>larceny</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OPRYLAND DR</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36.20999999970633</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L15" t="n">
-        <v>808.3</v>
+        <v>247.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 27, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 3. Case #20260453969 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260459134_11</t>
+          <t>DP2026415590230300</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46232.70902777778</v>
+        <v>46231.54236111111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HARRASSMENT (NUISANCE)</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>larceny</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TWO RIVERS PKWY</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>36.19000000021294</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K16" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L16" t="n">
-        <v>1455.9</v>
+        <v>247.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Harrassment (nuisance) on Jul 29, 2026, 1456 m from Opry Mills (TWO RIVERS PKWY). Premises: PARK. Status: OPEN. Victims: 1. Case #20260459134 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260452878_11</t>
+          <t>DP2026413635260700</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46229.60694444444</v>
+        <v>46230.58125</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2131 2131</t>
+          <t>2 N ADAMS ST</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>36.10599999977134</v>
+        <v>39.71654731730718</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.8170000000033</v>
+        <v>-104.9482864243138</v>
       </c>
       <c r="L17" t="n">
-        <v>191.2</v>
+        <v>384.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 191 m from The Mall at Green Hills (2131 2131). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260452878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260451477_11</t>
+          <t>DP20266010142239900</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46228.27083333334</v>
+        <v>46230.10416666666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BURGLARY</t>
+          <t>theft-other</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3717,56 +3725,56 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CHANNELKIRK LN</t>
+          <t>3444 E 2ND AVE</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>36.10999999969955</v>
+        <v>39.7193352135378</v>
       </c>
       <c r="K18" t="n">
-        <v>-86.81000000032267</v>
+        <v>-104.9468354191938</v>
       </c>
       <c r="L18" t="n">
-        <v>630.5</v>
+        <v>576.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Burglary on Jul 25, 2026, 631 m from The Mall at Green Hills (CHANNELKIRK LN). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260451477 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260453759_11</t>
+          <t>DP2026413301299900</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46229.95833333334</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3776,174 +3784,174 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2024 2024</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>36.09999999975003</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K19" t="n">
-        <v>-86.81499999983789</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L19" t="n">
-        <v>859.2</v>
+        <v>670.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 859 m from The Mall at Green Hills (2024 2024). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260453759 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260458322_11</t>
+          <t>DP20266010143299900</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46232.0625</v>
+        <v>46229.9375</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BURGLARY - MOTOR VEHICLE</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Unarmed</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HILLSBORO PIKE</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>36.09999999975003</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K20" t="n">
-        <v>-86.82000000025143</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L20" t="n">
-        <v>910.1</v>
+        <v>670.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Burglary - motor vehicle on Jul 29, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260458322 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20260450411_11</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46228.02083333334</v>
+        <v>46229.1125</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SIMPLE ASSLT</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PERSONAL (HANDS)</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HILLSBORO PIKE</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>36.09999999975003</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K21" t="n">
-        <v>-86.82000000025143</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L21" t="n">
-        <v>910.1</v>
+        <v>696.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Simple asslt on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: PERSONAL (HANDS). Premises: HIGHWAY, ROAD, ALLEY. Status: OPEN. Victims: 1. Case #20260450411 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260450256_11</t>
+          <t>DP2026415569230400</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46228.02569444444</v>
+        <v>46230.83333333334</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- &gt;$1,000 BUT &lt; $2,500</t>
+          <t>theft-parts-from-vehicle</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3951,54 +3959,58 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>theft-from-motor-vehicle</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HILLSBORO</t>
+          <t>441 N MILWAUKEE ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>36.09999999975003</v>
+        <v>39.72335589487053</v>
       </c>
       <c r="K22" t="n">
-        <v>-86.82000000025143</v>
+        <v>-104.9524528146586</v>
       </c>
       <c r="L22" t="n">
-        <v>910.1</v>
+        <v>722.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft of merchandise- &gt;$1,000 but &lt; $2,500 on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260450256 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-parts-from-vehicle on Jul 27, 2026, 722 m from Cherry Creek Shopping Center (441 N MILWAUKEE ST). Victims: 1. Case #DP2026415569 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20260449408_11</t>
+          <t>DP2026411500220400</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46227.61805555555</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>burglary-residence-no-force</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4008,56 +4020,56 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025 2025</t>
+          <t>100 BLK N GARFIELD ST</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>36.11399999985069</v>
+        <v>39.71871773048673</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.80900000023999</v>
+        <v>-104.9439679319565</v>
       </c>
       <c r="L23" t="n">
-        <v>969.2</v>
+        <v>779.5</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Lost property on Jul 24, 2026, 969 m from The Mall at Green Hills (2025 2025). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Case #20260449408 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>DP2026409833230500</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46228.56944444445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-items-from-vehicle</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4067,115 +4079,115 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>theft-from-motor-vehicle</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>373 S JACKSON ST</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>47.7086028</v>
+        <v>39.70992379075913</v>
       </c>
       <c r="K24" t="n">
-        <v>-122.324615154453</v>
+        <v>-104.9426513848476</v>
       </c>
       <c r="L24" t="n">
-        <v>145.2</v>
+        <v>1159</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-items-from-vehicle on Jul 25, 2026, 1159 m from Cherry Creek Shopping Center (373 S JACKSON ST). Victims: 1. Case #DP2026409833 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71909585262</t>
+          <t>20260725-2301-00</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Other Unlisted Non-Criminal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>899</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>6900 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.70858578</v>
+        <v>35.14684118006692</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.321918377919</v>
+        <v>-80.82544759809264</v>
       </c>
       <c r="L25" t="n">
-        <v>338.4</v>
+        <v>722.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
+          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71899643103</t>
+          <t>20260726-0712-02</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.78263888889</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4185,56 +4197,56 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>116XX BLOCK OF AURORA AVE N</t>
+          <t>6300 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>47.71354798</v>
+        <v>35.15641923337007</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.344834273165</v>
+        <v>-80.83429541207509</v>
       </c>
       <c r="L26" t="n">
-        <v>1511</v>
+        <v>613</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 1511 m from Northgate Station (116XX BLOCK OF AURORA AVE N). Case #2026-221622 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>20260726-0550-00</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46231.625</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4244,233 +4256,233 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>6700 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>47.7086028</v>
+        <v>35.1479657453291</v>
       </c>
       <c r="K27" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82922688152722</v>
       </c>
       <c r="L27" t="n">
-        <v>145.2</v>
+        <v>450.4</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>71890752645</t>
+          <t>20260725-0853-00</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46231.21458333333</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism of Property</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>5700 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>47.70668788</v>
+        <v>35.15368289092867</v>
       </c>
       <c r="K28" t="n">
-        <v>-122.311189989679</v>
+        <v>-80.8398453262274</v>
       </c>
       <c r="L28" t="n">
-        <v>1145.7</v>
+        <v>877.1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism of property on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>20260726-0657-00</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>5500 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>47.70668788</v>
+        <v>35.15375121029781</v>
       </c>
       <c r="K29" t="n">
-        <v>-122.311189997702</v>
+        <v>-80.83607576012871</v>
       </c>
       <c r="L29" t="n">
-        <v>1145.7</v>
+        <v>551.7</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>47.70668788</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K30" t="n">
-        <v>-122.311189997702</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L30" t="n">
-        <v>1145.7</v>
+        <v>178.9</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>71906728829</t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46231</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Theft of Motor Vehicle Parts or Accessories</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4480,233 +4492,233 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9XX BLOCK OF N 103RD ST</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>47.70360675</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K31" t="n">
-        <v>-122.346021623573</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L31" t="n">
-        <v>1551.2</v>
+        <v>178.9</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Theft of motor vehicle parts or accessories on Jul 28, 2026, 1551 m from Northgate Station (9XX BLOCK OF N 103RD ST). Case #2026-222196 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>47.70504225</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K32" t="n">
-        <v>-122.338094779232</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L32" t="n">
-        <v>938.8</v>
+        <v>178.9</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>71854915364</t>
+          <t>20260727-1945-02</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46228.91527777778</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Not Reportable to NIBRS</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>N 105TH ST / AURORA AVE N</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>47.70505121</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K33" t="n">
-        <v>-122.3446941292056</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L33" t="n">
-        <v>1411</v>
+        <v>178.9</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Not reportable to nibrs on Jul 25, 2026, 1411 m from Northgate Station (N 105TH ST / AURORA AVE N). Case #2026-218646 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>71896083189</t>
+          <t>20260726-1824-01</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46228.875</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NE 100TH ST / 5TH AVE NE</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>47.70132479</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K34" t="n">
-        <v>-122.3231272219471</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L34" t="n">
-        <v>785.6</v>
+        <v>178.9</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46227.5</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4716,56 +4728,56 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K35" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L35" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4775,233 +4787,233 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>39.7162154712797</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K36" t="n">
-        <v>-104.9512928115626</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L36" t="n">
-        <v>144.7</v>
+        <v>178.9</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>20260725-1137-00</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Suicide</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>801</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>5600 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>39.7162154712797</v>
+        <v>35.15235596527605</v>
       </c>
       <c r="K37" t="n">
-        <v>-104.9512928115626</v>
+        <v>-80.84558404556884</v>
       </c>
       <c r="L37" t="n">
-        <v>144.7</v>
+        <v>1376.8</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suicide on Jul 25, 2026, 1377 m from Southpark (5600 FAIRVIEW RD). Status: Open. Case #20260725-1137-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>20260726-0952-00</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>700 GOVERNOR MORRISON ST</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>39.71813319743836</v>
+        <v>35.15648042297118</v>
       </c>
       <c r="K38" t="n">
-        <v>-104.9522056316381</v>
+        <v>-80.82480681029648</v>
       </c>
       <c r="L38" t="n">
-        <v>148.6</v>
+        <v>723.7</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DP2026416370230300</t>
+          <t>20260725-0631-00</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Drug/Narcotic Violations</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>35A</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>8300 STEELE CREEK RD</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>39.71666393731682</v>
+        <v>35.17291837763486</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.9556403659223</v>
+        <v>-80.95939837774333</v>
       </c>
       <c r="L39" t="n">
-        <v>247.6</v>
+        <v>1070.3</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drug/narcotic violations on Jul 25, 2026, 1070 m from Charlotte Premium Outlets (8300 STEELE CREEK RD). Status: Open. Case #20260725-0631-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DP2026415590230300</t>
+          <t>20260725-1934-03</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>46231.54236111111</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5011,56 +5023,56 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>4900 TROJAN DR</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>39.71666393731682</v>
+        <v>35.16474336144204</v>
       </c>
       <c r="K40" t="n">
-        <v>-104.9556403659223</v>
+        <v>-80.96762879799847</v>
       </c>
       <c r="L40" t="n">
-        <v>247.6</v>
+        <v>443.5</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DP2026413635260700</t>
+          <t>20260729-1434-02</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>46230.58125</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Damage/Vandalism Of Property</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5070,56 +5082,56 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>290</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2 N ADAMS ST</t>
+          <t>5600 KELTONWOOD RD</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>39.71654731730718</v>
+        <v>35.16655081611235</v>
       </c>
       <c r="K41" t="n">
-        <v>-104.9482864243138</v>
+        <v>-80.97476086867614</v>
       </c>
       <c r="L41" t="n">
-        <v>384.1</v>
+        <v>496.6</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
+          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>INTLPLAZA:Tampa PD Crimes (365d)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DP20266010142239900</t>
+          <t>2026445724</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46230.10416666666</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>theft-other</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5129,351 +5141,343 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3444 E 2ND AVE</t>
+          <t>SR 60 W NB - Spruce Ramp &amp; Spruce-Airport Ramp</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>39.7193352135378</v>
+        <v>27.95994382970347</v>
       </c>
       <c r="K42" t="n">
-        <v>-104.9468354191938</v>
+        <v>-82.53472608010854</v>
       </c>
       <c r="L42" t="n">
-        <v>576.2</v>
+        <v>1534.5</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 29, 2026, 1535 m from International Plaza (SR 60 W NB - Spruce Ramp &amp; Spruce-Airport Ramp). Case #2026445724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DP2026413301299900</t>
+          <t>26C139724</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46229.95833333334</v>
+        <v>46227.69421296296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>BATTERY DV</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>39.71957373655755</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K43" t="n">
-        <v>-104.9597628432634</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L43" t="n">
-        <v>670.6</v>
+        <v>1122.4</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DP20266010143299900</t>
+          <t>26C140260</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46229.9375</v>
+        <v>46228.77152777778</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>39.71957373655755</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K44" t="n">
-        <v>-104.9597628432634</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L44" t="n">
-        <v>670.6</v>
+        <v>398.7</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>26C140486</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46229.1125</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>assault-simple</t>
-        </is>
-      </c>
+        <v>46228.51944444444</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>other-crimes-against-persons</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>39.71130989687384</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K45" t="n">
-        <v>-104.9490029653731</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L45" t="n">
-        <v>696.3</v>
+        <v>398.7</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DP2026411500220400</t>
+          <t>26C143336</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46229.08333333334</v>
+        <v>46232.7125</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>burglary-residence-no-force</t>
+          <t>TRESPASS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>burglary</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100 BLK N GARFIELD ST</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>39.71871773048673</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K46" t="n">
-        <v>-104.9439679319565</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L46" t="n">
-        <v>779.5</v>
+        <v>398.7</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
+          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DP2026409833230500</t>
+          <t>26C143989</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46228.56944444445</v>
+        <v>46233.61180555556</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>theft-items-from-vehicle</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>theft-from-motor-vehicle</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>373 S JACKSON ST</t>
+          <t>700 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>39.70992379075913</v>
+        <v>37.67384327067582</v>
       </c>
       <c r="K47" t="n">
-        <v>-104.9426513848476</v>
+        <v>-97.25634062142737</v>
       </c>
       <c r="L47" t="n">
-        <v>1159</v>
+        <v>1259.5</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Theft-items-from-vehicle on Jul 25, 2026, 1159 m from Cherry Creek Shopping Center (373 S JACKSON ST). Victims: 1. Case #DP2026409833 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1260 m from Towne East Square (700 BLOCK OF S APACHE DR). Case #26C143989 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260725-2301-00</t>
+          <t>26C144045</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46233.65833333333</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Other Unlisted Non-Criminal</t>
+          <t>DEAD BODIES FOUND NO WITNESS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5483,56 +5487,56 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>SUDDEN_DEATH</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6900 FAIRVIEW RD</t>
+          <t>700 BLOCK OF S EASTRIDGE DR</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>35.14684118006692</v>
+        <v>37.67625582907724</v>
       </c>
       <c r="K48" t="n">
-        <v>-80.82544759809264</v>
+        <v>-97.25926072916232</v>
       </c>
       <c r="L48" t="n">
-        <v>722.6</v>
+        <v>1264.7</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Dead bodies found no witness on Jul 30, 2026, 1265 m from Towne East Square (700 BLOCK OF S EASTRIDGE DR). Case #26C144045 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260726-0712-02</t>
+          <t>26C520577</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46227.71388888889</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5542,56 +5546,56 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>SUSP_CHARAC</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6300 CARNEGIE BV</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>35.15641923337007</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K49" t="n">
-        <v>-80.83429541207509</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L49" t="n">
-        <v>613</v>
+        <v>398.7</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260726-0550-00</t>
+          <t>26C520675</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46227.84236111111</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5601,528 +5605,520 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6700 FAIRVIEW RD</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>35.1479657453291</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K50" t="n">
-        <v>-80.82922688152722</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L50" t="n">
-        <v>450.4</v>
+        <v>398.7</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260725-0853-00</t>
+          <t>26C520776</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.45833333334</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>AUTO THEFT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>AUTOTHEFT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5700 CARNEGIE BV</t>
+          <t>500 BLOCK OF N ROCK RD</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>35.15368289092867</v>
+        <v>37.6938385342284</v>
       </c>
       <c r="K51" t="n">
-        <v>-80.8398453262274</v>
+        <v>-97.24455420498546</v>
       </c>
       <c r="L51" t="n">
-        <v>877.1</v>
+        <v>1264</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Auto theft on Jul 26, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520776 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260726-0657-00</t>
+          <t>26C139922</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46227.95277777778</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5500 CARNEGIE BV</t>
+          <t>7000 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>35.15375121029781</v>
+        <v>37.67195398477438</v>
       </c>
       <c r="K52" t="n">
-        <v>-80.83607576012871</v>
+        <v>-97.25533959083543</v>
       </c>
       <c r="L52" t="n">
-        <v>551.7</v>
+        <v>1383.4</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t>26C140815</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.30625</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>900 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67195267201163</v>
       </c>
       <c r="K53" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.25741761429009</v>
       </c>
       <c r="L53" t="n">
-        <v>178.9</v>
+        <v>1484.1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 26, 2026, 1484 m from Towne East Square (900 BLOCK OF S APACHE DR). Case #26C140815 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>26C142785</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46231.96458333333</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>EVADE POLICE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>DRIVING_VIO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>E KELLOGG DR &amp; S ROCK RD</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67911842691625</v>
       </c>
       <c r="K54" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.24451202953301</v>
       </c>
       <c r="L54" t="n">
-        <v>178.9</v>
+        <v>473.3</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>26C142917</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46232.18194444444</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>WINDOWPEEPING</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>SEX_OFFENSES1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K55" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L55" t="n">
-        <v>178.9</v>
+        <v>1285.1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Windowpeeping on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C142917 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20260727-1945-02</t>
+          <t>26C141216</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.90069444444</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>CHECKED WELFARE OF A CHILD</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>FAMILY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>7300 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67974587023429</v>
       </c>
       <c r="K56" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.25225228651782</v>
       </c>
       <c r="L56" t="n">
-        <v>178.9</v>
+        <v>537.4</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20260726-1824-01</t>
+          <t>26C143148</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46229.16666666666</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>All Other Offenses</t>
-        </is>
-      </c>
+        <v>46232.52430555555</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>90Z</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>900 BLOCK OF S ENOCH DR</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67197658912259</v>
       </c>
       <c r="K57" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.2456018407935</v>
       </c>
       <c r="L57" t="n">
-        <v>178.9</v>
+        <v>1203</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 29, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C143148 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>26C141683</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46230.58541666667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>MISC OFFICERS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>OUTSIDE_CASE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>8100 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.15120046375475</v>
+        <v>37.6797148529391</v>
       </c>
       <c r="K58" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.24233946631864</v>
       </c>
       <c r="L58" t="n">
-        <v>178.9</v>
+        <v>556.7</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>26C143446</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46232.7125</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6132,115 +6128,115 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K59" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L59" t="n">
-        <v>178.9</v>
+        <v>398.7</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20260725-1137-00</t>
+          <t>26C144013</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46233.63055555556</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5600 FAIRVIEW RD</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>35.15235596527605</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K60" t="n">
-        <v>-80.84558404556884</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L60" t="n">
-        <v>1376.8</v>
+        <v>398.7</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Suicide on Jul 25, 2026, 1377 m from Southpark (5600 FAIRVIEW RD). Status: Open. Case #20260725-1137-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20260726-0952-00</t>
+          <t>26C144067</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46232.71180555555</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>All Other Offenses</t>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6250,203 +6246,203 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>90Z</t>
+          <t>TRAFFIC</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>700 GOVERNOR MORRISON ST</t>
+          <t>8000 BLOCK OF E DOUGLAS AVE</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>35.15648042297118</v>
+        <v>37.6865673723019</v>
       </c>
       <c r="K61" t="n">
-        <v>-80.82480681029648</v>
+        <v>-97.24449812404205</v>
       </c>
       <c r="L61" t="n">
-        <v>723.7</v>
+        <v>501</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20260725-0631-00</t>
+          <t>26C142294</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46231.42847222222</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Drug/Narcotic Violations</t>
+          <t>FOUND MISC PROPERTY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>35A</t>
+          <t>FOUND_PROP</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8300 STEELE CREEK RD</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>35.17291837763486</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K62" t="n">
-        <v>-80.95939837774333</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L62" t="n">
-        <v>1070.3</v>
+        <v>1251.5</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Drug/narcotic violations on Jul 25, 2026, 1070 m from Charlotte Premium Outlets (8300 STEELE CREEK RD). Status: Open. Case #20260725-0631-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Found misc property on Jul 28, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142294 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20260725-1934-03</t>
+          <t>26C144131</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46233.7625</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4900 TROJAN DR</t>
+          <t>E BAYLEY ST &amp; S GOVERNEOUR RD</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>35.16474336144204</v>
+        <v>37.67014134415807</v>
       </c>
       <c r="K63" t="n">
-        <v>-80.96762879799847</v>
+        <v>-97.25360392908074</v>
       </c>
       <c r="L63" t="n">
-        <v>443.5</v>
+        <v>1498.8</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1499 m from Towne East Square (E BAYLEY ST &amp; S GOVERNEOUR RD). Case #26C144131 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20260729-1434-02</t>
+          <t>26C143812</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46232.88888888889</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Damage/Vandalism Of Property</t>
+          <t>OTV-HIT AND RUN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>OTHERTRAF_VIO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5600 KELTONWOOD RD</t>
+          <t>400 BLOCK OF S ROCK RD</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>35.16655081611235</v>
+        <v>37.68150034571348</v>
       </c>
       <c r="K64" t="n">
-        <v>-80.97476086867614</v>
+        <v>-97.24450622724754</v>
       </c>
       <c r="L64" t="n">
-        <v>496.6</v>
+        <v>288.9</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6468,44 +6464,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26C139456</t>
+          <t>26C144101</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>46227.42226851852</v>
+        <v>46233.72152777778</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER BURGLARY UNIT</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SUSP_CHARAC</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7200 BLOCK OF E LINCOLN ST</t>
+          <t>600 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>37.67196805016872</v>
+        <v>37.67516836949827</v>
       </c>
       <c r="K65" t="n">
-        <v>-97.25239793155058</v>
+        <v>-97.25367616461408</v>
       </c>
       <c r="L65" t="n">
-        <v>1271.2</v>
+        <v>1002.3</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Suspicious character burglary unit on Jul 24, 2026, 1271 m from Towne East Square (7200 BLOCK OF E LINCOLN ST). Case #26C139456 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1002 m from Towne East Square (600 BLOCK OF S APACHE DR). Case #26C144101 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6527,44 +6523,36 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26C139724</t>
+          <t>26C139706</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46227.69421296296</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>BATTERY DV</t>
-        </is>
-      </c>
+        <v>46227.66875</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S EASTERN AVE</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>37.6774046653855</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K66" t="n">
-        <v>-97.23656061094495</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L66" t="n">
-        <v>1122.4</v>
+        <v>398.7</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6586,44 +6574,44 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26C140260</t>
+          <t>26C141863</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>46228.77152777778</v>
+        <v>46230.75486111111</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>RUNAWAY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K67" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L67" t="n">
-        <v>398.7</v>
+        <v>1285.1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
+          <t>Runaway on Jul 27, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C141863 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6645,36 +6633,44 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>26C140486</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46228.51944444444</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
+        <v>46230.75</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>BATTERY ABW</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>37.67911394923933</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K68" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L68" t="n">
-        <v>398.7</v>
+        <v>1251.5</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6696,44 +6692,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26C143336</t>
+          <t>26C142387</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46230.81597222222</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TRESPASS</t>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MISC_OFFENSES</t>
+          <t>TRAFFIC</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>100 BLOCK OF S ROCK RD</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>37.67911394923933</v>
+        <v>37.6865673723019</v>
       </c>
       <c r="K69" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.24449812404205</v>
       </c>
       <c r="L69" t="n">
-        <v>398.7</v>
+        <v>501</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
+          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6755,15 +6751,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>26C143989</t>
+          <t>26C142657</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46233.61180555556</v>
+        <v>46231.79166666666</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t>INTERFERENCE W PARENTAL CUSTODY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6773,26 +6769,26 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MISC_REPORT</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S APACHE DR</t>
+          <t>900 BLOCK OF S ENOCH DR</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>37.67384327067582</v>
+        <v>37.67197658912259</v>
       </c>
       <c r="K70" t="n">
-        <v>-97.25634062142737</v>
+        <v>-97.2456018407935</v>
       </c>
       <c r="L70" t="n">
-        <v>1259.5</v>
+        <v>1203</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Misc report on Jul 30, 2026, 1260 m from Towne East Square (700 BLOCK OF S APACHE DR). Case #26C143989 (use for a records request — full narratives are not published in open data).</t>
+          <t>Interference w parental custody on Jul 28, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C142657 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6814,15 +6810,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>26C144045</t>
+          <t>26C142768</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>46233.65833333333</v>
+        <v>46231.94305555556</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DEAD BODIES FOUND NO WITNESS</t>
+          <t>CHECKED WELFARE OF A CHILD</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6832,26 +6828,26 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SUDDEN_DEATH</t>
+          <t>FAMILY</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S EASTRIDGE DR</t>
+          <t>6500 BLOCK OF E MORRIS ST</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>37.67625582907724</v>
+        <v>37.67377815761698</v>
       </c>
       <c r="K71" t="n">
-        <v>-97.25926072916232</v>
+        <v>-97.2605034310844</v>
       </c>
       <c r="L71" t="n">
-        <v>1264.7</v>
+        <v>1519.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Dead bodies found no witness on Jul 30, 2026, 1265 m from Towne East Square (700 BLOCK OF S EASTRIDGE DR). Case #26C144045 (use for a records request — full narratives are not published in open data).</t>
+          <t>Checked welfare of a child on Jul 28, 2026, 1520 m from Towne East Square (6500 BLOCK OF E MORRIS ST). Case #26C142768 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6873,44 +6869,44 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26C520577</t>
+          <t>26C143218</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46227.71388888889</v>
+        <v>46232.58333333334</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
+          <t>DISTURB THE PEACE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SUSP_CHARAC</t>
+          <t>DISORDERLY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K72" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L72" t="n">
-        <v>398.7</v>
+        <v>1285.1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
+          <t>Disturb the peace on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C143218 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6932,44 +6928,44 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>26C520675</t>
+          <t>26C143562</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46227.84236111111</v>
+        <v>46232.93958333333</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>MENTAL CASES</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>MENTAL_CASE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>37.67911394923933</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K73" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L73" t="n">
-        <v>398.7</v>
+        <v>1122.4</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
+          <t>Mental cases on Jul 29, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C143562 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6991,44 +6987,44 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>26C520776</t>
+          <t>26C143576</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46229.45833333334</v>
+        <v>46232.96111111111</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AUTO THEFT</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>AUTOTHEFT</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>500 BLOCK OF N ROCK RD</t>
+          <t>7500 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>37.6938385342284</v>
+        <v>37.67197300274878</v>
       </c>
       <c r="K74" t="n">
-        <v>-97.24455420498546</v>
+        <v>-97.24902708647107</v>
       </c>
       <c r="L74" t="n">
-        <v>1264</v>
+        <v>1201.1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Auto theft on Jul 26, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520776 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 29, 2026, 1201 m from Towne East Square (7500 BLOCK OF E LINCOLN ST). Case #26C143576 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7050,15 +7046,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26C139721</t>
+          <t>26C143936</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46227.625</v>
+        <v>46233.55972222222</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OTV-HIT AND RUN</t>
+          <t>POSSESSION OF PARAPHERNALIA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7068,26 +7064,26 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>OTHERTRAF_VIO</t>
+          <t>DRUGS</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>E LINCOLN ST &amp; S ROCK RD</t>
+          <t>500 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>37.67198361320128</v>
+        <v>37.67912059117884</v>
       </c>
       <c r="K75" t="n">
-        <v>-97.24446143278816</v>
+        <v>-97.25894321098265</v>
       </c>
       <c r="L75" t="n">
-        <v>1219.7</v>
+        <v>1089.5</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Otv-hit and run on Jul 24, 2026, 1220 m from Towne East Square (E LINCOLN ST &amp; S ROCK RD). Case #26C139721 (use for a records request — full narratives are not published in open data).</t>
+          <t>Possession of paraphernalia on Jul 30, 2026, 1090 m from Towne East Square (500 BLOCK OF S HUNTER ST). Case #26C143936 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7109,44 +7105,44 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26C139922</t>
+          <t>26C520567</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46227.95277777778</v>
+        <v>46227.6875</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>LARCENY B FROM AUTO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7000 BLOCK OF E LINCOLN ST</t>
+          <t>7200 BLOCK OF E BAYLEY ST</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>37.67195398477438</v>
+        <v>37.67101904846645</v>
       </c>
       <c r="K76" t="n">
-        <v>-97.25533959083543</v>
+        <v>-97.25239274309988</v>
       </c>
       <c r="L76" t="n">
-        <v>1383.4</v>
+        <v>1370.6</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b from auto on Jul 24, 2026, 1371 m from Towne East Square (7200 BLOCK OF E BAYLEY ST). Case #26C520567 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7168,15 +7164,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>26C140815</t>
+          <t>26C520979</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46229.30625</v>
+        <v>46231.94583333333</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t>SUSPICIOUS CHARACTER SIB UNIT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7186,26 +7182,26 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MISC_REPORT</t>
+          <t>SUSP_CHARAC</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>900 BLOCK OF S APACHE DR</t>
+          <t>500 BLOCK OF N ROCK RD</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>37.67195267201163</v>
+        <v>37.6938385342284</v>
       </c>
       <c r="K77" t="n">
-        <v>-97.25741761429009</v>
+        <v>-97.24455420498546</v>
       </c>
       <c r="L77" t="n">
-        <v>1484.1</v>
+        <v>1264</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Misc report on Jul 26, 2026, 1484 m from Towne East Square (900 BLOCK OF S APACHE DR). Case #26C140815 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character sib unit on Jul 28, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520979 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7227,44 +7223,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26C142785</t>
+          <t>26C520282</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46231.96458333333</v>
+        <v>46231.625</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>EVADE POLICE</t>
+          <t>LOST MISC PROPERTY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DRIVING_VIO</t>
+          <t>LOST_PROPERTY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>E KELLOGG DR &amp; S ROCK RD</t>
+          <t>7000 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>37.67911842691625</v>
+        <v>37.67951495831583</v>
       </c>
       <c r="K78" t="n">
-        <v>-97.24451202953301</v>
+        <v>-97.25782989544317</v>
       </c>
       <c r="L78" t="n">
-        <v>473.3</v>
+        <v>982.3</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
+          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7286,44 +7282,44 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26C142917</t>
+          <t>26C520741</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46232.18194444444</v>
+        <v>46228.86111111111</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>WINDOWPEEPING</t>
+          <t>LARCENY B AUTO ACCESSORIES</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SEX_OFFENSES1</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S HUNTER ST</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>37.67688443377517</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K79" t="n">
-        <v>-97.26003808987583</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L79" t="n">
-        <v>1285.1</v>
+        <v>398.7</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Windowpeeping on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C142917 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7345,44 +7341,44 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26C141216</t>
+          <t>26C520933</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>46229.90069444444</v>
+        <v>46230.6125</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CHECKED WELFARE OF A CHILD</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FAMILY</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7300 BLOCK OF E KELLOGG ST</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>37.67974587023429</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K80" t="n">
-        <v>-97.25225228651782</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L80" t="n">
-        <v>537.4</v>
+        <v>398.7</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7404,302 +7400,294 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26C143148</t>
+          <t>26C521105</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46232.52430555555</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
+        <v>46233.075</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>REVOCATION SUSP DL</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>900 BLOCK OF S ENOCH DR</t>
+          <t>700 BLOCK OF S WOODLAWN BLVD</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>37.67197658912259</v>
+        <v>37.67556302964613</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.2456018407935</v>
+        <v>-97.26215557703324</v>
       </c>
       <c r="L81" t="n">
-        <v>1203</v>
+        <v>1520.5</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Incident on Jul 29, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C143148 (use for a records request — full narratives are not published in open data).</t>
+          <t>Revocation susp dl on Jul 30, 2026, 1520 m from Towne East Square (700 BLOCK OF S WOODLAWN BLVD). Case #26C521105 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>26C141683</t>
+          <t xml:space="preserve">TE202675652         </t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>46230.58541666667</v>
+        <v>46230.77569444444</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MISC OFFICERS</t>
+          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>OUTSIDE_CASE</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8100 BLOCK OF E KELLOGG ST</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>37.6797148529391</v>
+        <v>33.38314167531927</v>
       </c>
       <c r="K82" t="n">
-        <v>-97.24233946631864</v>
+        <v>-111.9645674529712</v>
       </c>
       <c r="L82" t="n">
-        <v>556.7</v>
+        <v>14.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>26C143446</t>
+          <t xml:space="preserve">TE202674996         </t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46228.65694444445</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38314167531927</v>
       </c>
       <c r="K83" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9645674529712</v>
       </c>
       <c r="L83" t="n">
-        <v>398.7</v>
+        <v>14.7</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>26C144013</t>
+          <t xml:space="preserve">TE202674783         </t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46233.63055555556</v>
+        <v>46227.91319444445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38314167531927</v>
       </c>
       <c r="K84" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9645674529712</v>
       </c>
       <c r="L84" t="n">
-        <v>398.7</v>
+        <v>14.7</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26C144067</t>
+          <t xml:space="preserve">TE202675415         </t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46232.71180555555</v>
+        <v>46229.95</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>TRAFFIC</t>
-        </is>
-      </c>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8000 BLOCK OF E DOUGLAS AVE</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>37.6865673723019</v>
+        <v>33.38341075529574</v>
       </c>
       <c r="K85" t="n">
-        <v>-97.24449812404205</v>
+        <v>-111.9652490281131</v>
       </c>
       <c r="L85" t="n">
-        <v>501</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
+          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26C142294</t>
+          <t xml:space="preserve">TE202675399         </t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>46231.42847222222</v>
+        <v>46229.9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FOUND MISC PROPERTY</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7707,176 +7695,164 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>FOUND_PROP</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>37.6756469679485</v>
+        <v>33.38552975305072</v>
       </c>
       <c r="K86" t="n">
-        <v>-97.25850032865422</v>
+        <v>-111.965328834686</v>
       </c>
       <c r="L86" t="n">
-        <v>1251.5</v>
+        <v>262</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Found misc property on Jul 28, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142294 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26C144131</t>
+          <t xml:space="preserve">TE202676101         </t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>46233.7625</v>
+        <v>46232.21041666667</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>E BAYLEY ST &amp; S GOVERNEOUR RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>37.67014134415807</v>
+        <v>33.38580430470485</v>
       </c>
       <c r="K87" t="n">
-        <v>-97.25360392908074</v>
+        <v>-111.9660628528483</v>
       </c>
       <c r="L87" t="n">
-        <v>1498.8</v>
+        <v>315.7</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Misc report on Jul 30, 2026, 1499 m from Towne East Square (E BAYLEY ST &amp; S GOVERNEOUR RD). Case #26C144131 (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>26C143812</t>
+          <t xml:space="preserve">TE202676030         </t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>46232.88888888889</v>
+        <v>46231.83194444444</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>OTV-HIT AND RUN</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>OTHERTRAF_VIO</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>400 BLOCK OF S ROCK RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>37.68150034571348</v>
+        <v>33.3805974892332</v>
       </c>
       <c r="K88" t="n">
-        <v>-97.24450622724754</v>
+        <v>-111.9623154538272</v>
       </c>
       <c r="L88" t="n">
-        <v>288.9</v>
+        <v>361.4</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>26C139586</t>
+          <t xml:space="preserve">TE202674893         </t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>46227.55138888889</v>
+        <v>46228.35972222222</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7884,58 +7860,54 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S EASTERN AVE</t>
+          <t>4XXX S WENDLER DR</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>37.6774046653855</v>
+        <v>33.38130369903515</v>
       </c>
       <c r="K89" t="n">
-        <v>-97.23656061094495</v>
+        <v>-111.9695754725762</v>
       </c>
       <c r="L89" t="n">
-        <v>1122.4</v>
+        <v>517</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Misc report on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139586 (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26C144101</t>
+          <t xml:space="preserve">TE202675649         </t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>46233.72152777778</v>
+        <v>46230.76944444444</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7943,54 +7915,50 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S APACHE DR</t>
+          <t>4XXX S DARROW DR</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>37.67516836949827</v>
+        <v>33.38128291577831</v>
       </c>
       <c r="K90" t="n">
-        <v>-97.25367616461408</v>
+        <v>-111.9593051545489</v>
       </c>
       <c r="L90" t="n">
-        <v>1002.3</v>
+        <v>533.1</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Misc report on Jul 30, 2026, 1002 m from Towne East Square (600 BLOCK OF S APACHE DR). Case #26C144101 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>26C139706</t>
+          <t xml:space="preserve">TE202676505         </t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>46227.66875</v>
+        <v>46233.33055555556</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
@@ -8001,287 +7969,267 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>PRIEST DR / W US 60</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38739758078362</v>
       </c>
       <c r="K91" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9609102222452</v>
       </c>
       <c r="L91" t="n">
-        <v>398.7</v>
+        <v>568.9</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 30, 2026, 569 m from Arizona Mills (PRIEST DR / W US 60). Case #TE202676505          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26C141863</t>
+          <t xml:space="preserve">TE202676469         </t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>46230.75486111111</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>RUNAWAY</t>
-        </is>
-      </c>
+        <v>46233.21041666667</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>MISC_OFFENSES</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S HUNTER ST</t>
+          <t>4XXX S PRIEST DR</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>37.67688443377517</v>
+        <v>33.38356449694355</v>
       </c>
       <c r="K92" t="n">
-        <v>-97.26003808987583</v>
+        <v>-111.9581399763744</v>
       </c>
       <c r="L92" t="n">
-        <v>1285.1</v>
+        <v>594.2</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Runaway on Jul 27, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C141863 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 30, 2026, 594 m from Arizona Mills (4XXX S PRIEST DR). Case #TE202676469          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t xml:space="preserve">TE2026601265        </t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>46230.75</v>
+        <v>46229.48611111111</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t xml:space="preserve">[23C] SHOPLIFTING                                                               </t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>37.6756469679485</v>
+        <v>33.37921050936001</v>
       </c>
       <c r="K93" t="n">
-        <v>-97.25850032865422</v>
+        <v>-111.9595924257048</v>
       </c>
       <c r="L93" t="n">
-        <v>1251.5</v>
+        <v>643.4</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>[23c] shoplifting on Jul 26, 2026, 643 m from Arizona Mills (1XXX W BASELINE RD). Case #TE2026601265         (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26C142387</t>
+          <t xml:space="preserve">TE202675235         </t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>46230.81597222222</v>
+        <v>46229.31597222222</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>TRAFFIC</t>
-        </is>
-      </c>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>100 BLOCK OF S ROCK RD</t>
+          <t>BASELINE RD / I10</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>37.6865673723019</v>
+        <v>33.37824262058852</v>
       </c>
       <c r="K94" t="n">
-        <v>-97.24449812404205</v>
+        <v>-111.9680044627475</v>
       </c>
       <c r="L94" t="n">
-        <v>501</v>
+        <v>645.4</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>26C142657</t>
+          <t xml:space="preserve">TE202675001         </t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>46231.79166666666</v>
+        <v>46228.66944444444</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>INTERFERENCE W PARENTAL CUSTODY</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>MISC_OFFENSES</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>900 BLOCK OF S ENOCH DR</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>37.67197658912259</v>
+        <v>33.377865729326</v>
       </c>
       <c r="K95" t="n">
-        <v>-97.2456018407935</v>
+        <v>-111.9618554026273</v>
       </c>
       <c r="L95" t="n">
-        <v>1203</v>
+        <v>650.2</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Interference w parental custody on Jul 28, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C142657 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>26C142768</t>
+          <t xml:space="preserve">TE202676035         </t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>46231.94305555556</v>
+        <v>46231.85555555556</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CHECKED WELFARE OF A CHILD</t>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8289,117 +8237,109 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>FAMILY</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>6500 BLOCK OF E MORRIS ST</t>
+          <t>1XXX W LA JOLLA DR</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>37.67377815761698</v>
+        <v>33.38909587497265</v>
       </c>
       <c r="K96" t="n">
-        <v>-97.2605034310844</v>
+        <v>-111.961540133513</v>
       </c>
       <c r="L96" t="n">
-        <v>1519.9</v>
+        <v>704.8</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Checked welfare of a child on Jul 28, 2026, 1520 m from Towne East Square (6500 BLOCK OF E MORRIS ST). Case #26C142768 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>26C143218</t>
+          <t xml:space="preserve">TE202675946         </t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>46232.58333333334</v>
+        <v>46231.63888888889</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>DISTURB THE PEACE</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>DISORDERLY</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S HUNTER ST</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>37.67688443377517</v>
+        <v>33.37795738260824</v>
       </c>
       <c r="K97" t="n">
-        <v>-97.26003808987583</v>
+        <v>-111.959149564986</v>
       </c>
       <c r="L97" t="n">
-        <v>1285.1</v>
+        <v>773.7</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Disturb the peace on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C143218 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>26C143562</t>
+          <t xml:space="preserve">TE202674935         </t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>46232.93958333333</v>
+        <v>46228.47222222222</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MENTAL CASES</t>
+          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8407,117 +8347,109 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>MENTAL_CASE</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S EASTERN AVE</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>37.6774046653855</v>
+        <v>33.37594547787401</v>
       </c>
       <c r="K98" t="n">
-        <v>-97.23656061094495</v>
+        <v>-111.9593287567214</v>
       </c>
       <c r="L98" t="n">
-        <v>1122.4</v>
+        <v>946.9</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Mental cases on Jul 29, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C143562 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>26C143576</t>
+          <t xml:space="preserve">TE202674869         </t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>46232.96111111111</v>
+        <v>46228.26388888889</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[SC-0] LOST - PROPERTY (NON-FIREARM, OTHER THAN GOV'T ISSUED ID)                </t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7500 BLOCK OF E LINCOLN ST</t>
+          <t>PARKSIDE DR / W FREMONT DR</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>37.67197300274878</v>
+        <v>33.38169955020192</v>
       </c>
       <c r="K99" t="n">
-        <v>-97.24902708647107</v>
+        <v>-111.954283203492</v>
       </c>
       <c r="L99" t="n">
-        <v>1201.1</v>
+        <v>967.3</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Misc report on Jul 29, 2026, 1201 m from Towne East Square (7500 BLOCK OF E LINCOLN ST). Case #26C143576 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>26C143936</t>
+          <t xml:space="preserve">TE2026601259        </t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>46233.55972222222</v>
+        <v>46229.58055555556</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>POSSESSION OF PARAPHERNALIA</t>
+          <t xml:space="preserve">[0] CRIMINAL DAMAGE - UNDER $1000                                               </t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8525,117 +8457,109 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>DRUGS</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>500 BLOCK OF S HUNTER ST</t>
+          <t>1XXX W SOUTHERN AVE</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>37.67912059117884</v>
+        <v>33.39259581629993</v>
       </c>
       <c r="K100" t="n">
-        <v>-97.25894321098265</v>
+        <v>-111.9580558007179</v>
       </c>
       <c r="L100" t="n">
-        <v>1089.5</v>
+        <v>1198.6</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Possession of paraphernalia on Jul 30, 2026, 1090 m from Towne East Square (500 BLOCK OF S HUNTER ST). Case #26C143936 (use for a records request — full narratives are not published in open data).</t>
+          <t>[0] criminal damage - under $1000 on Jul 26, 2026, 1199 m from Arizona Mills (1XXX W SOUTHERN AVE). Case #TE2026601259         (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>26C520567</t>
+          <t xml:space="preserve">TE202676006         </t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>46227.6875</v>
+        <v>46231.77708333333</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LARCENY B FROM AUTO</t>
+          <t xml:space="preserve">[GO-0] DEATH                                                                    </t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>7200 BLOCK OF E BAYLEY ST</t>
+          <t>2XXX W SOUTHERN AVE</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>37.67101904846645</v>
+        <v>33.38855944643347</v>
       </c>
       <c r="K101" t="n">
-        <v>-97.25239274309988</v>
+        <v>-111.9758211943486</v>
       </c>
       <c r="L101" t="n">
-        <v>1370.6</v>
+        <v>1202.1</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Larceny b from auto on Jul 24, 2026, 1371 m from Towne East Square (7200 BLOCK OF E BAYLEY ST). Case #26C520567 (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] death on Jul 28, 2026, 1202 m from Arizona Mills (2XXX W SOUTHERN AVE). Case #TE202676006          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>26C520979</t>
+          <t xml:space="preserve">TE202674741         </t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>46231.94583333333</v>
+        <v>46227.81666666667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER SIB UNIT</t>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8643,264 +8567,244 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>SUSP_CHARAC</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>500 BLOCK OF N ROCK RD</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>37.6938385342284</v>
+        <v>33.37634047797651</v>
       </c>
       <c r="K102" t="n">
-        <v>-97.24455420498546</v>
+        <v>-111.9531278046354</v>
       </c>
       <c r="L102" t="n">
-        <v>1264</v>
+        <v>1309.4</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Suspicious character sib unit on Jul 28, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520979 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674741          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>26C520282</t>
+          <t xml:space="preserve">TE202674714         </t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>46231.625</v>
+        <v>46227.7375</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LOST MISC PROPERTY</t>
+          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>LOST_PROPERTY</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>7000 BLOCK OF E KELLOGG ST</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>37.67951495831583</v>
+        <v>33.37634047797651</v>
       </c>
       <c r="K103" t="n">
-        <v>-97.25782989544317</v>
+        <v>-111.9531278046354</v>
       </c>
       <c r="L103" t="n">
-        <v>982.3</v>
+        <v>1309.4</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>26C520741</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>46228.86111111111</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LARCENY B AUTO ACCESSORIES</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>37.67911394923933</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K104" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L104" t="n">
-        <v>398.7</v>
+        <v>1345.1</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>26C520933</t>
+          <t xml:space="preserve">TE202676025         </t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>46230.6125</v>
+        <v>46231.82430555556</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t xml:space="preserve">[SC-0] WARRANT - BOOKED INTO DETENTION                                          </t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>7XXX S 48TH ST</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38154948911996</v>
       </c>
       <c r="K105" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9788828064167</v>
       </c>
       <c r="L105" t="n">
-        <v>398.7</v>
+        <v>1346.3</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] warrant - booked into detention on Jul 28, 2026, 1346 m from Arizona Mills (7XXX S 48TH ST). Case #TE202676025          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>26C521105</t>
+          <t xml:space="preserve">TE202674804         </t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>46233.075</v>
+        <v>46227.98263888889</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>REVOCATION SUSP DL</t>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>OTHERTRAF_VIO</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S WOODLAWN BLVD</t>
+          <t>MCKEMY ST / S HARDY DR</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>37.67556302964613</v>
+        <v>33.37562594922362</v>
       </c>
       <c r="K106" t="n">
-        <v>-97.26215557703324</v>
+        <v>-111.9529211309643</v>
       </c>
       <c r="L106" t="n">
-        <v>1520.5</v>
+        <v>1372.7</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Revocation susp dl on Jul 30, 2026, 1520 m from Towne East Square (700 BLOCK OF S WOODLAWN BLVD). Case #26C521105 (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 24, 2026, 1373 m from Arizona Mills (MCKEMY ST / S HARDY DR). Case #TE202674804          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -8922,40 +8826,40 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675652         </t>
+          <t xml:space="preserve">TE202675422         </t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>46230.77569444444</v>
+        <v>46229.96111111111</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>3XXX S 52ND ST</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>33.38314167531927</v>
+        <v>33.3959248712565</v>
       </c>
       <c r="K107" t="n">
-        <v>-111.9645674529712</v>
+        <v>-111.9704886613678</v>
       </c>
       <c r="L107" t="n">
-        <v>14.7</v>
+        <v>1512</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] info - information other (non-criminal) on Jul 26, 2026, 1512 m from Arizona Mills (3XXX S 52ND ST). Case #TE202675422          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -8977,17 +8881,13 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674996         </t>
+          <t xml:space="preserve">TE202674830         </t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>46228.65694444445</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
-        </is>
-      </c>
+        <v>46228.05902777778</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>OTHER</t>
@@ -8996,21 +8896,21 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>SOUTHERN AVE / S HARDY DR</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>33.38314167531927</v>
+        <v>33.39284504948579</v>
       </c>
       <c r="K108" t="n">
-        <v>-111.9645674529712</v>
+        <v>-111.9519846600515</v>
       </c>
       <c r="L108" t="n">
-        <v>14.7</v>
+        <v>1578</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 25, 2026, 1578 m from Arizona Mills (SOUTHERN AVE / S HARDY DR). Case #TE202674830          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -9032,1416 +8932,45 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674783         </t>
+          <t xml:space="preserve">TE202675096         </t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>46227.91319444445</v>
+        <v>46228.88680555556</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t xml:space="preserve">[11D] MOLESTATION OF A CHILD                                                    </t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7XX W BASELINE RD</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>33.38314167531927</v>
+        <v>33.37881261615141</v>
       </c>
       <c r="K109" t="n">
-        <v>-111.9645674529712</v>
+        <v>-111.9483590935493</v>
       </c>
       <c r="L109" t="n">
-        <v>14.7</v>
+        <v>1581.2</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675415         </t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>46229.95</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>33.38341075529574</v>
-      </c>
-      <c r="K110" t="n">
-        <v>-111.9652490281131</v>
-      </c>
-      <c r="L110" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675399         </t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>46229.9</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>33.38552975305072</v>
-      </c>
-      <c r="K111" t="n">
-        <v>-111.965328834686</v>
-      </c>
-      <c r="L111" t="n">
-        <v>262</v>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676101         </t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>46232.21041666667</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>33.38580430470485</v>
-      </c>
-      <c r="K112" t="n">
-        <v>-111.9660628528483</v>
-      </c>
-      <c r="L112" t="n">
-        <v>315.7</v>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676030         </t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>46231.83194444444</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>33.3805974892332</v>
-      </c>
-      <c r="K113" t="n">
-        <v>-111.9623154538272</v>
-      </c>
-      <c r="L113" t="n">
-        <v>361.4</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674893         </t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>46228.35972222222</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>4XXX S WENDLER DR</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>33.38130369903515</v>
-      </c>
-      <c r="K114" t="n">
-        <v>-111.9695754725762</v>
-      </c>
-      <c r="L114" t="n">
-        <v>517</v>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675649         </t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>46230.76944444444</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>4XXX S DARROW DR</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>33.38128291577831</v>
-      </c>
-      <c r="K115" t="n">
-        <v>-111.9593051545489</v>
-      </c>
-      <c r="L115" t="n">
-        <v>533.1</v>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674654         </t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>46227.62708333333</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] ACCIDENT - HIT AND RUN                                                   </t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>BASELINE RD / S DARROW DR</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>33.37825351544224</v>
-      </c>
-      <c r="K116" t="n">
-        <v>-111.9611381808533</v>
-      </c>
-      <c r="L116" t="n">
-        <v>640.6</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675235         </t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>46229.31597222222</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>BASELINE RD / I10</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>33.37824262058852</v>
-      </c>
-      <c r="K117" t="n">
-        <v>-111.9680044627475</v>
-      </c>
-      <c r="L117" t="n">
-        <v>645.4</v>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675001         </t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>46228.66944444444</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1XXX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>33.377865729326</v>
-      </c>
-      <c r="K118" t="n">
-        <v>-111.9618554026273</v>
-      </c>
-      <c r="L118" t="n">
-        <v>650.2</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676035         </t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>46231.85555555556</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1XXX W LA JOLLA DR</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>33.38909587497265</v>
-      </c>
-      <c r="K119" t="n">
-        <v>-111.961540133513</v>
-      </c>
-      <c r="L119" t="n">
-        <v>704.8</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675946         </t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>46231.63888888889</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1XXX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>33.37795738260824</v>
-      </c>
-      <c r="K120" t="n">
-        <v>-111.959149564986</v>
-      </c>
-      <c r="L120" t="n">
-        <v>773.7</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674935         </t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>46228.47222222222</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1XXX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>33.37594547787401</v>
-      </c>
-      <c r="K121" t="n">
-        <v>-111.9593287567214</v>
-      </c>
-      <c r="L121" t="n">
-        <v>946.9</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674869         </t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>46228.26388888889</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] LOST - PROPERTY (NON-FIREARM, OTHER THAN GOV'T ISSUED ID)                </t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>PARKSIDE DR / W FREMONT DR</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>33.38169955020192</v>
-      </c>
-      <c r="K122" t="n">
-        <v>-111.954283203492</v>
-      </c>
-      <c r="L122" t="n">
-        <v>967.3</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674568         </t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>46227.44722222222</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>9XX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>33.37784058487316</v>
-      </c>
-      <c r="K123" t="n">
-        <v>-111.9548908569819</v>
-      </c>
-      <c r="L123" t="n">
-        <v>1079.6</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 24, 2026, 1080 m from Arizona Mills (9XX W BASELINE RD). Case #TE202674568          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE2026601259        </t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>46229.58055555556</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[0] CRIMINAL DAMAGE - UNDER $1000                                               </t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1XXX W SOUTHERN AVE</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>33.39259581629993</v>
-      </c>
-      <c r="K124" t="n">
-        <v>-111.9580558007179</v>
-      </c>
-      <c r="L124" t="n">
-        <v>1198.6</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>[0] criminal damage - under $1000 on Jul 26, 2026, 1199 m from Arizona Mills (1XXX W SOUTHERN AVE). Case #TE2026601259         (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676006         </t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>46231.77708333333</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] DEATH                                                                    </t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2XXX W SOUTHERN AVE</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>33.38855944643347</v>
-      </c>
-      <c r="K125" t="n">
-        <v>-111.9758211943486</v>
-      </c>
-      <c r="L125" t="n">
-        <v>1202.1</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>[go-0] death on Jul 28, 2026, 1202 m from Arizona Mills (2XXX W SOUTHERN AVE). Case #TE202676006          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674741         </t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>46227.81666666667</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>33.37634047797651</v>
-      </c>
-      <c r="K126" t="n">
-        <v>-111.9531278046354</v>
-      </c>
-      <c r="L126" t="n">
-        <v>1309.4</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674741          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674557         </t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>46227.4125</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] WARNING - DISORDERLY CONDUCT                                             </t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>33.37634047797651</v>
-      </c>
-      <c r="K127" t="n">
-        <v>-111.9531278046354</v>
-      </c>
-      <c r="L127" t="n">
-        <v>1309.4</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>[sc-0] warning - disorderly conduct on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674557          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674714         </t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>46227.7375</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J128" t="n">
-        <v>33.37634047797651</v>
-      </c>
-      <c r="K128" t="n">
-        <v>-111.9531278046354</v>
-      </c>
-      <c r="L128" t="n">
-        <v>1309.4</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675136         </t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>46228.97847222222</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J129" t="n">
-        <v>33.3757495513233</v>
-      </c>
-      <c r="K129" t="n">
-        <v>-111.9531832468173</v>
-      </c>
-      <c r="L129" t="n">
-        <v>1345.1</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676025         </t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>46231.82430555556</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] WARRANT - BOOKED INTO DETENTION                                          </t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>7XXX S 48TH ST</t>
-        </is>
-      </c>
-      <c r="J130" t="n">
-        <v>33.38154948911996</v>
-      </c>
-      <c r="K130" t="n">
-        <v>-111.9788828064167</v>
-      </c>
-      <c r="L130" t="n">
-        <v>1346.3</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>[sc-0] warrant - booked into detention on Jul 28, 2026, 1346 m from Arizona Mills (7XXX S 48TH ST). Case #TE202676025          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674804         </t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>46227.98263888889</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>MCKEMY ST / S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J131" t="n">
-        <v>33.37562594922362</v>
-      </c>
-      <c r="K131" t="n">
-        <v>-111.9529211309643</v>
-      </c>
-      <c r="L131" t="n">
-        <v>1372.7</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>[240] motor vehicle theft on Jul 24, 2026, 1373 m from Arizona Mills (MCKEMY ST / S HARDY DR). Case #TE202674804          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675422         </t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>46229.96111111111</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3XXX S 52ND ST</t>
-        </is>
-      </c>
-      <c r="J132" t="n">
-        <v>33.3959248712565</v>
-      </c>
-      <c r="K132" t="n">
-        <v>-111.9704886613678</v>
-      </c>
-      <c r="L132" t="n">
-        <v>1512</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 26, 2026, 1512 m from Arizona Mills (3XXX S 52ND ST). Case #TE202675422          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674830         </t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>46228.05902777778</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>SOUTHERN AVE / S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
-        <v>33.39284504948579</v>
-      </c>
-      <c r="K133" t="n">
-        <v>-111.9519846600515</v>
-      </c>
-      <c r="L133" t="n">
-        <v>1578</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>Incident on Jul 25, 2026, 1578 m from Arizona Mills (SOUTHERN AVE / S HARDY DR). Case #TE202674830          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675096         </t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>46228.88680555556</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[11D] MOLESTATION OF A CHILD                                                    </t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>7XX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>33.37881261615141</v>
-      </c>
-      <c r="K134" t="n">
-        <v>-111.9483590935493</v>
-      </c>
-      <c r="L134" t="n">
-        <v>1581.2</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
           <t>[11d] molestation of a child on Jul 25, 2026, 1581 m from Arizona Mills (7XX W BASELINE RD). Case #TE202675096          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M134"/>
+  <autoFilter ref="A1:M109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10479,7 +9008,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:45:48.319120+00:00</t>
+          <t>2026-07-31 15:12:36.086883+00:00</t>
         </is>
       </c>
     </row>
@@ -10511,7 +9040,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 07:45:48.319120+00:00</t>
+          <t>2026-07-24 15:12:36.086883+00:00</t>
         </is>
       </c>
     </row>
@@ -10522,7 +9051,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -10567,7 +9096,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OK fetched=15 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10579,7 +9108,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OK fetched=9 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10591,7 +9120,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OK fetched=12 truncated=False</t>
+          <t>OK fetched=11 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10603,7 +9132,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OK fetched=12 truncated=False</t>
+          <t>OK fetched=13 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10651,7 +9180,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OK fetched=0 truncated=False</t>
+          <t>OK fetched=1 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10675,7 +9204,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OK fetched=28 truncated=False</t>
+          <t>OK fetched=31 truncated=False</t>
         </is>
       </c>
     </row>
